--- a/research/traditional_assets/database/data/bangladesh/bangladesh_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/bangladesh/bangladesh_drugs_biotechnology.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1799474655384197</v>
+        <v>0.1794391231418044</v>
       </c>
       <c r="C2">
-        <v>12.12222409779293</v>
+        <v>12.04178506235493</v>
       </c>
       <c r="D2">
-        <v>11.21522409779293</v>
+        <v>11.25788506235493</v>
       </c>
       <c r="E2">
-        <v>-3.649999999999999</v>
+        <v>-3.526899999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1231</v>
       </c>
       <c r="G2">
         <v>0.907</v>
@@ -1451,28 +1451,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006191929999999999</v>
       </c>
       <c r="N2">
-        <v>2.513333333333334</v>
+        <v>2.507141403333334</v>
       </c>
       <c r="O2">
-        <v>0.7540000000000001</v>
+        <v>0.7521424210000001</v>
       </c>
       <c r="P2">
-        <v>1.759333333333334</v>
+        <v>1.754998982333334</v>
       </c>
       <c r="Q2">
-        <v>4.679333333333334</v>
+        <v>4.674998982333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1799474655384197</v>
+        <v>0.1808959829715196</v>
       </c>
       <c r="T2">
-        <v>1.149078177305102</v>
+        <v>1.157202972498169</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>405.9046748482838</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1794391231418044</v>
+        <v>0.1789307807451892</v>
       </c>
       <c r="C3">
-        <v>12.04178506235493</v>
+        <v>11.96167181749437</v>
       </c>
       <c r="D3">
-        <v>11.25788506235493</v>
+        <v>11.30087181749437</v>
       </c>
       <c r="E3">
-        <v>-3.526899999999999</v>
+        <v>-3.403799999999999</v>
       </c>
       <c r="F3">
-        <v>0.1231</v>
+        <v>0.2462</v>
       </c>
       <c r="G3">
         <v>0.907</v>
@@ -1533,28 +1533,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M3">
-        <v>0.006191929999999999</v>
+        <v>0.01238386</v>
       </c>
       <c r="N3">
-        <v>2.507141403333334</v>
+        <v>2.500949473333334</v>
       </c>
       <c r="O3">
-        <v>0.7521424210000001</v>
+        <v>0.7502848420000001</v>
       </c>
       <c r="P3">
-        <v>1.754998982333334</v>
+        <v>1.750664631333334</v>
       </c>
       <c r="Q3">
-        <v>4.674998982333333</v>
+        <v>4.670664631333334</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1808959829715196</v>
+        <v>0.1818638579032543</v>
       </c>
       <c r="T3">
-        <v>1.157202972498169</v>
+        <v>1.165493579838032</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>405.9046748482838</v>
+        <v>202.9523374241419</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1789307807451892</v>
+        <v>0.1784224383485739</v>
       </c>
       <c r="C4">
-        <v>11.96167181749437</v>
+        <v>11.88188810948147</v>
       </c>
       <c r="D4">
-        <v>11.30087181749437</v>
+        <v>11.34418810948146</v>
       </c>
       <c r="E4">
-        <v>-3.403799999999999</v>
+        <v>-3.2807</v>
       </c>
       <c r="F4">
-        <v>0.2462</v>
+        <v>0.3693</v>
       </c>
       <c r="G4">
         <v>0.907</v>
@@ -1615,28 +1615,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M4">
-        <v>0.01238386</v>
+        <v>0.01857579</v>
       </c>
       <c r="N4">
-        <v>2.500949473333334</v>
+        <v>2.494757543333334</v>
       </c>
       <c r="O4">
-        <v>0.7502848420000001</v>
+        <v>0.7484272630000001</v>
       </c>
       <c r="P4">
-        <v>1.750664631333334</v>
+        <v>1.746330280333334</v>
       </c>
       <c r="Q4">
-        <v>4.670664631333334</v>
+        <v>4.666330280333334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1818638579032543</v>
+        <v>0.1828516890191484</v>
       </c>
       <c r="T4">
-        <v>1.165493579838032</v>
+        <v>1.173955127535419</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>202.9523374241419</v>
+        <v>135.3015582827613</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1784224383485739</v>
+        <v>0.1779140959519586</v>
       </c>
       <c r="C5">
-        <v>11.88188810948147</v>
+        <v>11.80243774224529</v>
       </c>
       <c r="D5">
-        <v>11.34418810948146</v>
+        <v>11.38783774224529</v>
       </c>
       <c r="E5">
-        <v>-3.2807</v>
+        <v>-3.1576</v>
       </c>
       <c r="F5">
-        <v>0.3693</v>
+        <v>0.4923999999999999</v>
       </c>
       <c r="G5">
         <v>0.907</v>
@@ -1697,28 +1697,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M5">
-        <v>0.01857579</v>
+        <v>0.02476772</v>
       </c>
       <c r="N5">
-        <v>2.494757543333334</v>
+        <v>2.488565613333334</v>
       </c>
       <c r="O5">
-        <v>0.7484272630000001</v>
+        <v>0.7465696840000001</v>
       </c>
       <c r="P5">
-        <v>1.746330280333334</v>
+        <v>1.741995929333334</v>
       </c>
       <c r="Q5">
-        <v>4.666330280333334</v>
+        <v>4.661995929333333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1828516890191484</v>
+        <v>0.1838600999499569</v>
       </c>
       <c r="T5">
-        <v>1.173955127535419</v>
+        <v>1.182592957476501</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>135.3015582827613</v>
+        <v>101.476168712071</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1779140959519586</v>
+        <v>0.1774057535553434</v>
       </c>
       <c r="C6">
-        <v>11.80243774224529</v>
+        <v>11.7233245784874</v>
       </c>
       <c r="D6">
-        <v>11.38783774224529</v>
+        <v>11.4318245784874</v>
       </c>
       <c r="E6">
-        <v>-3.1576</v>
+        <v>-3.0345</v>
       </c>
       <c r="F6">
-        <v>0.4923999999999999</v>
+        <v>0.6154999999999999</v>
       </c>
       <c r="G6">
         <v>0.907</v>
@@ -1779,28 +1779,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M6">
-        <v>0.02476772</v>
+        <v>0.03095964999999999</v>
       </c>
       <c r="N6">
-        <v>2.488565613333334</v>
+        <v>2.482373683333334</v>
       </c>
       <c r="O6">
-        <v>0.7465696840000001</v>
+        <v>0.7447121050000002</v>
       </c>
       <c r="P6">
-        <v>1.741995929333334</v>
+        <v>1.737661578333334</v>
       </c>
       <c r="Q6">
-        <v>4.661995929333333</v>
+        <v>4.657661578333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1838600999499569</v>
+        <v>0.184889740584572</v>
       </c>
       <c r="T6">
-        <v>1.182592957476501</v>
+        <v>1.191412636468974</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>101.476168712071</v>
+        <v>81.18093496965678</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1774057535553434</v>
+        <v>0.1768974111587281</v>
       </c>
       <c r="C7">
-        <v>11.7233245784874</v>
+        <v>11.64455254082129</v>
       </c>
       <c r="D7">
-        <v>11.4318245784874</v>
+        <v>11.47615254082129</v>
       </c>
       <c r="E7">
-        <v>-3.0345</v>
+        <v>-2.9114</v>
       </c>
       <c r="F7">
-        <v>0.6154999999999999</v>
+        <v>0.7386</v>
       </c>
       <c r="G7">
         <v>0.907</v>
@@ -1861,28 +1861,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M7">
-        <v>0.03095964999999999</v>
+        <v>0.03715158</v>
       </c>
       <c r="N7">
-        <v>2.482373683333334</v>
+        <v>2.476181753333333</v>
       </c>
       <c r="O7">
-        <v>0.7447121050000002</v>
+        <v>0.742854526</v>
       </c>
       <c r="P7">
-        <v>1.737661578333334</v>
+        <v>1.733327227333334</v>
       </c>
       <c r="Q7">
-        <v>4.657661578333334</v>
+        <v>4.653327227333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.184889740584572</v>
+        <v>0.1859412884667321</v>
       </c>
       <c r="T7">
-        <v>1.191412636468974</v>
+        <v>1.200419968205968</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>81.18093496965678</v>
+        <v>67.65077914138062</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1768974111587281</v>
+        <v>0.1763890687621129</v>
       </c>
       <c r="C8">
-        <v>11.64455254082129</v>
+        <v>11.56612561293845</v>
       </c>
       <c r="D8">
-        <v>11.47615254082129</v>
+        <v>11.52082561293845</v>
       </c>
       <c r="E8">
-        <v>-2.9114</v>
+        <v>-2.7883</v>
       </c>
       <c r="F8">
-        <v>0.7385999999999999</v>
+        <v>0.8616999999999998</v>
       </c>
       <c r="G8">
         <v>0.907</v>
@@ -1943,28 +1943,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M8">
-        <v>0.03715158</v>
+        <v>0.04334350999999999</v>
       </c>
       <c r="N8">
-        <v>2.476181753333333</v>
+        <v>2.469989823333334</v>
       </c>
       <c r="O8">
-        <v>0.742854526</v>
+        <v>0.7409969470000001</v>
       </c>
       <c r="P8">
-        <v>1.733327227333334</v>
+        <v>1.728992876333333</v>
       </c>
       <c r="Q8">
-        <v>4.653327227333333</v>
+        <v>4.648992876333333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1859412884667321</v>
+        <v>0.1870154502818418</v>
       </c>
       <c r="T8">
-        <v>1.200419968205968</v>
+        <v>1.209621006001823</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>67.65077914138062</v>
+        <v>57.9863821211834</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1763890687621129</v>
+        <v>0.1758807263654977</v>
       </c>
       <c r="C9">
-        <v>11.56612561293845</v>
+        <v>11.48804784080187</v>
       </c>
       <c r="D9">
-        <v>11.52082561293845</v>
+        <v>11.56584784080187</v>
       </c>
       <c r="E9">
-        <v>-2.7883</v>
+        <v>-2.6652</v>
       </c>
       <c r="F9">
-        <v>0.8617</v>
+        <v>0.9847999999999999</v>
       </c>
       <c r="G9">
         <v>0.907</v>
@@ -2025,28 +2025,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M9">
-        <v>0.04334351</v>
+        <v>0.04953543999999999</v>
       </c>
       <c r="N9">
-        <v>2.469989823333334</v>
+        <v>2.463797893333334</v>
       </c>
       <c r="O9">
-        <v>0.7409969470000001</v>
+        <v>0.739139368</v>
       </c>
       <c r="P9">
-        <v>1.728992876333333</v>
+        <v>1.724658525333334</v>
       </c>
       <c r="Q9">
-        <v>4.648992876333333</v>
+        <v>4.644658525333334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1870154502818418</v>
+        <v>0.1881129634407583</v>
       </c>
       <c r="T9">
-        <v>1.209621006001823</v>
+        <v>1.219022066358456</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>57.98638212118339</v>
+        <v>50.73808435603547</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1758807263654977</v>
+        <v>0.1753723839688824</v>
       </c>
       <c r="C10">
-        <v>11.48804784080187</v>
+        <v>11.41032333386754</v>
       </c>
       <c r="D10">
-        <v>11.56584784080187</v>
+        <v>11.61122333386754</v>
       </c>
       <c r="E10">
-        <v>-2.6652</v>
+        <v>-2.5421</v>
       </c>
       <c r="F10">
-        <v>0.9847999999999999</v>
+        <v>1.1079</v>
       </c>
       <c r="G10">
         <v>0.907</v>
@@ -2107,28 +2107,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M10">
-        <v>0.04953543999999999</v>
+        <v>0.05572736999999999</v>
       </c>
       <c r="N10">
-        <v>2.463797893333334</v>
+        <v>2.457605963333334</v>
       </c>
       <c r="O10">
-        <v>0.739139368</v>
+        <v>0.7372817890000001</v>
       </c>
       <c r="P10">
-        <v>1.724658525333334</v>
+        <v>1.720324174333334</v>
       </c>
       <c r="Q10">
-        <v>4.644658525333334</v>
+        <v>4.640324174333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1881129634407583</v>
+        <v>0.1892345977680026</v>
       </c>
       <c r="T10">
-        <v>1.219022066358456</v>
+        <v>1.228629743426225</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>50.73808435603547</v>
+        <v>45.10051942758709</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1753723839688824</v>
+        <v>0.1748640415722671</v>
       </c>
       <c r="C11">
-        <v>11.41032333386754</v>
+        <v>11.33295626633478</v>
       </c>
       <c r="D11">
-        <v>11.61122333386754</v>
+        <v>11.65695626633478</v>
       </c>
       <c r="E11">
-        <v>-2.5421</v>
+        <v>-2.419</v>
       </c>
       <c r="F11">
-        <v>1.1079</v>
+        <v>1.231</v>
       </c>
       <c r="G11">
         <v>0.907</v>
@@ -2189,28 +2189,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M11">
-        <v>0.05572736999999999</v>
+        <v>0.06191929999999999</v>
       </c>
       <c r="N11">
-        <v>2.457605963333334</v>
+        <v>2.451414033333334</v>
       </c>
       <c r="O11">
-        <v>0.7372817890000001</v>
+        <v>0.73542421</v>
       </c>
       <c r="P11">
-        <v>1.720324174333334</v>
+        <v>1.715989823333333</v>
       </c>
       <c r="Q11">
-        <v>4.640324174333333</v>
+        <v>4.635989823333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1892345977680026</v>
+        <v>0.190381157302519</v>
       </c>
       <c r="T11">
-        <v>1.228629743426225</v>
+        <v>1.238450924428832</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>45.10051942758709</v>
+        <v>40.59046748482838</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1748640415722671</v>
+        <v>0.1743556991756519</v>
       </c>
       <c r="C12">
-        <v>11.33295626633478</v>
+        <v>11.25595087842639</v>
       </c>
       <c r="D12">
-        <v>11.65695626633478</v>
+        <v>11.70305087842639</v>
       </c>
       <c r="E12">
-        <v>-2.419</v>
+        <v>-2.2959</v>
       </c>
       <c r="F12">
-        <v>1.231</v>
+        <v>1.3541</v>
       </c>
       <c r="G12">
         <v>0.907</v>
@@ -2271,28 +2271,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M12">
-        <v>0.06191929999999999</v>
+        <v>0.06811122999999999</v>
       </c>
       <c r="N12">
-        <v>2.451414033333334</v>
+        <v>2.445222103333334</v>
       </c>
       <c r="O12">
-        <v>0.73542421</v>
+        <v>0.7335666310000001</v>
       </c>
       <c r="P12">
-        <v>1.715989823333333</v>
+        <v>1.711655472333334</v>
       </c>
       <c r="Q12">
-        <v>4.635989823333333</v>
+        <v>4.631655472333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.190381157302519</v>
+        <v>0.1915534822198336</v>
       </c>
       <c r="T12">
-        <v>1.238450924428832</v>
+        <v>1.248492806128128</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>40.59046748482838</v>
+        <v>36.90042498620762</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1743556991756519</v>
+        <v>0.1738473567790366</v>
       </c>
       <c r="C13">
-        <v>11.25595087842639</v>
+        <v>11.17931147769917</v>
       </c>
       <c r="D13">
-        <v>11.70305087842639</v>
+        <v>11.74951147769917</v>
       </c>
       <c r="E13">
-        <v>-2.2959</v>
+        <v>-2.1728</v>
       </c>
       <c r="F13">
-        <v>1.3541</v>
+        <v>1.4772</v>
       </c>
       <c r="G13">
         <v>0.907</v>
@@ -2353,28 +2353,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M13">
-        <v>0.06811122999999999</v>
+        <v>0.07430315999999999</v>
       </c>
       <c r="N13">
-        <v>2.445222103333334</v>
+        <v>2.439030173333334</v>
       </c>
       <c r="O13">
-        <v>0.7335666310000001</v>
+        <v>0.7317090520000001</v>
       </c>
       <c r="P13">
-        <v>1.711655472333334</v>
+        <v>1.707321121333333</v>
       </c>
       <c r="Q13">
-        <v>4.631655472333334</v>
+        <v>4.627321121333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1915534822198336</v>
+        <v>0.1927524508852689</v>
       </c>
       <c r="T13">
-        <v>1.248492806128128</v>
+        <v>1.258762912411498</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>36.90042498620762</v>
+        <v>33.82538957069032</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1738473567790366</v>
+        <v>0.1733390143824213</v>
       </c>
       <c r="C14">
-        <v>11.17931147769917</v>
+        <v>11.10304244038579</v>
       </c>
       <c r="D14">
-        <v>11.74951147769917</v>
+        <v>11.79634244038579</v>
       </c>
       <c r="E14">
-        <v>-2.1728</v>
+        <v>-2.0497</v>
       </c>
       <c r="F14">
-        <v>1.4772</v>
+        <v>1.6003</v>
       </c>
       <c r="G14">
         <v>0.907</v>
@@ -2435,28 +2435,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M14">
-        <v>0.07430315999999999</v>
+        <v>0.08049508999999999</v>
       </c>
       <c r="N14">
-        <v>2.439030173333334</v>
+        <v>2.432838243333334</v>
       </c>
       <c r="O14">
-        <v>0.7317090520000001</v>
+        <v>0.7298514730000001</v>
       </c>
       <c r="P14">
-        <v>1.707321121333333</v>
+        <v>1.702986770333334</v>
       </c>
       <c r="Q14">
-        <v>4.627321121333333</v>
+        <v>4.622986770333334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1927524508852689</v>
+        <v>0.1939789820487602</v>
       </c>
       <c r="T14">
-        <v>1.258762912411498</v>
+        <v>1.269269113092188</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>33.82538957069032</v>
+        <v>31.22343652679106</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1733390143824213</v>
+        <v>0.1728306719858061</v>
       </c>
       <c r="C15">
-        <v>11.10304244038579</v>
+        <v>11.02714821276894</v>
       </c>
       <c r="D15">
-        <v>11.79634244038579</v>
+        <v>11.84354821276894</v>
       </c>
       <c r="E15">
-        <v>-2.0497</v>
+        <v>-1.926599999999999</v>
       </c>
       <c r="F15">
-        <v>1.6003</v>
+        <v>1.7234</v>
       </c>
       <c r="G15">
         <v>0.907</v>
@@ -2517,28 +2517,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M15">
-        <v>0.08049508999999999</v>
+        <v>0.08668702</v>
       </c>
       <c r="N15">
-        <v>2.432838243333334</v>
+        <v>2.426646313333334</v>
       </c>
       <c r="O15">
-        <v>0.7298514730000001</v>
+        <v>0.7279938940000001</v>
       </c>
       <c r="P15">
-        <v>1.702986770333334</v>
+        <v>1.698652419333334</v>
       </c>
       <c r="Q15">
-        <v>4.622986770333334</v>
+        <v>4.618652419333333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1939789820487602</v>
+        <v>0.1952340371927978</v>
       </c>
       <c r="T15">
-        <v>1.269269113092188</v>
+        <v>1.280019644021265</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>31.22343652679106</v>
+        <v>28.9931910605917</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1728306719858061</v>
+        <v>0.1723223295891908</v>
       </c>
       <c r="C16">
-        <v>11.02714821276894</v>
+        <v>10.95163331258852</v>
       </c>
       <c r="D16">
-        <v>11.84354821276894</v>
+        <v>11.89113331258852</v>
       </c>
       <c r="E16">
-        <v>-1.926599999999999</v>
+        <v>-1.803499999999999</v>
       </c>
       <c r="F16">
-        <v>1.7234</v>
+        <v>1.8465</v>
       </c>
       <c r="G16">
         <v>0.907</v>
@@ -2599,28 +2599,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M16">
-        <v>0.08668702</v>
+        <v>0.09287895</v>
       </c>
       <c r="N16">
-        <v>2.426646313333334</v>
+        <v>2.420454383333334</v>
       </c>
       <c r="O16">
-        <v>0.7279938940000001</v>
+        <v>0.7261363150000001</v>
       </c>
       <c r="P16">
-        <v>1.698652419333334</v>
+        <v>1.694318068333334</v>
       </c>
       <c r="Q16">
-        <v>4.618652419333333</v>
+        <v>4.614318068333334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1952340371927978</v>
+        <v>0.1965186230461068</v>
       </c>
       <c r="T16">
-        <v>1.280019644021265</v>
+        <v>1.291023128619262</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>28.9931910605917</v>
+        <v>27.06031165655225</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1723223295891908</v>
+        <v>0.1718139871925755</v>
       </c>
       <c r="C17">
-        <v>10.95163331258852</v>
+        <v>10.87650233048298</v>
       </c>
       <c r="D17">
-        <v>11.89113331258852</v>
+        <v>11.93910233048298</v>
       </c>
       <c r="E17">
-        <v>-1.8035</v>
+        <v>-1.6804</v>
       </c>
       <c r="F17">
-        <v>1.8465</v>
+        <v>1.9696</v>
       </c>
       <c r="G17">
         <v>0.907</v>
@@ -2681,28 +2681,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M17">
-        <v>0.09287894999999999</v>
+        <v>0.09907087999999999</v>
       </c>
       <c r="N17">
-        <v>2.420454383333334</v>
+        <v>2.414262453333333</v>
       </c>
       <c r="O17">
-        <v>0.7261363150000001</v>
+        <v>0.724278736</v>
       </c>
       <c r="P17">
-        <v>1.694318068333334</v>
+        <v>1.689983717333333</v>
       </c>
       <c r="Q17">
-        <v>4.614318068333334</v>
+        <v>4.609983717333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1965186230461068</v>
+        <v>0.1978337942768756</v>
       </c>
       <c r="T17">
-        <v>1.291023128619262</v>
+        <v>1.302288600945782</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>27.06031165655225</v>
+        <v>25.36904217801774</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1718139871925755</v>
+        <v>0.1713056447959603</v>
       </c>
       <c r="C18">
-        <v>10.87650233048298</v>
+        <v>10.80175993146562</v>
       </c>
       <c r="D18">
-        <v>11.93910233048298</v>
+        <v>11.98745993146562</v>
       </c>
       <c r="E18">
-        <v>-1.6804</v>
+        <v>-1.5573</v>
       </c>
       <c r="F18">
-        <v>1.9696</v>
+        <v>2.0927</v>
       </c>
       <c r="G18">
         <v>0.907</v>
@@ -2763,28 +2763,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M18">
-        <v>0.09907087999999999</v>
+        <v>0.10526281</v>
       </c>
       <c r="N18">
-        <v>2.414262453333333</v>
+        <v>2.408070523333333</v>
       </c>
       <c r="O18">
-        <v>0.724278736</v>
+        <v>0.722421157</v>
       </c>
       <c r="P18">
-        <v>1.689983717333333</v>
+        <v>1.685649366333334</v>
       </c>
       <c r="Q18">
-        <v>4.609983717333334</v>
+        <v>4.605649366333333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1978337942768756</v>
+        <v>0.1991806563806751</v>
       </c>
       <c r="T18">
-        <v>1.302288600945782</v>
+        <v>1.313825530436798</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>25.36904217801774</v>
+        <v>23.87674557931081</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1713056447959603</v>
+        <v>0.170797302399345</v>
       </c>
       <c r="C19">
-        <v>10.80175993146562</v>
+        <v>10.72741085643696</v>
       </c>
       <c r="D19">
-        <v>11.98745993146562</v>
+        <v>12.03621085643696</v>
       </c>
       <c r="E19">
-        <v>-1.5573</v>
+        <v>-1.434199999999999</v>
       </c>
       <c r="F19">
-        <v>2.0927</v>
+        <v>2.2158</v>
       </c>
       <c r="G19">
         <v>0.907</v>
@@ -2845,28 +2845,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M19">
-        <v>0.10526281</v>
+        <v>0.11145474</v>
       </c>
       <c r="N19">
-        <v>2.408070523333333</v>
+        <v>2.401878593333334</v>
       </c>
       <c r="O19">
-        <v>0.722421157</v>
+        <v>0.720563578</v>
       </c>
       <c r="P19">
-        <v>1.685649366333334</v>
+        <v>1.681315015333333</v>
       </c>
       <c r="Q19">
-        <v>4.605649366333333</v>
+        <v>4.601315015333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1991806563806751</v>
+        <v>0.2005603687796891</v>
       </c>
       <c r="T19">
-        <v>1.313825530436798</v>
+        <v>1.325643848451984</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>23.87674557931081</v>
+        <v>22.55025971379354</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1707973023993451</v>
+        <v>0.1702889600027298</v>
       </c>
       <c r="C20">
-        <v>10.72741085643696</v>
+        <v>10.65345992373412</v>
       </c>
       <c r="D20">
-        <v>12.03621085643696</v>
+        <v>12.08535992373412</v>
       </c>
       <c r="E20">
-        <v>-1.4342</v>
+        <v>-1.3111</v>
       </c>
       <c r="F20">
-        <v>2.2158</v>
+        <v>2.3389</v>
       </c>
       <c r="G20">
         <v>0.907</v>
@@ -2927,28 +2927,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M20">
-        <v>0.11145474</v>
+        <v>0.11764667</v>
       </c>
       <c r="N20">
-        <v>2.401878593333334</v>
+        <v>2.395686663333334</v>
       </c>
       <c r="O20">
-        <v>0.720563578</v>
+        <v>0.7187059990000001</v>
       </c>
       <c r="P20">
-        <v>1.681315015333333</v>
+        <v>1.676980664333334</v>
       </c>
       <c r="Q20">
-        <v>4.601315015333333</v>
+        <v>4.596980664333334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2005603687796891</v>
+        <v>0.2019741481515182</v>
       </c>
       <c r="T20">
-        <v>1.325643848451984</v>
+        <v>1.337753976788532</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.55025971379354</v>
+        <v>21.36340393938336</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1702889600027298</v>
+        <v>0.1697806176061145</v>
       </c>
       <c r="C21">
-        <v>10.65345992373412</v>
+        <v>10.57991203071835</v>
       </c>
       <c r="D21">
-        <v>12.08535992373412</v>
+        <v>12.13491203071835</v>
       </c>
       <c r="E21">
-        <v>-1.3111</v>
+        <v>-1.188</v>
       </c>
       <c r="F21">
-        <v>2.3389</v>
+        <v>2.462</v>
       </c>
       <c r="G21">
         <v>0.907</v>
@@ -3009,28 +3009,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M21">
-        <v>0.11764667</v>
+        <v>0.1238386</v>
       </c>
       <c r="N21">
-        <v>2.395686663333334</v>
+        <v>2.389494733333334</v>
       </c>
       <c r="O21">
-        <v>0.7187059990000001</v>
+        <v>0.71684842</v>
       </c>
       <c r="P21">
-        <v>1.676980664333334</v>
+        <v>1.672646313333334</v>
       </c>
       <c r="Q21">
-        <v>4.596980664333334</v>
+        <v>4.592646313333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2019741481515182</v>
+        <v>0.2034232720076432</v>
       </c>
       <c r="T21">
-        <v>1.337753976788532</v>
+        <v>1.350166858333495</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.36340393938336</v>
+        <v>20.29523374241419</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1697806176061145</v>
+        <v>0.1692722752094993</v>
       </c>
       <c r="C22">
-        <v>10.57991203071835</v>
+        <v>10.50677215540176</v>
       </c>
       <c r="D22">
-        <v>12.13491203071835</v>
+        <v>12.18487215540176</v>
       </c>
       <c r="E22">
-        <v>-1.188</v>
+        <v>-1.064899999999999</v>
       </c>
       <c r="F22">
-        <v>2.462</v>
+        <v>2.5851</v>
       </c>
       <c r="G22">
         <v>0.907</v>
@@ -3091,28 +3091,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M22">
-        <v>0.1238386</v>
+        <v>0.13003053</v>
       </c>
       <c r="N22">
-        <v>2.389494733333334</v>
+        <v>2.383302803333334</v>
       </c>
       <c r="O22">
-        <v>0.71684842</v>
+        <v>0.7149908410000001</v>
       </c>
       <c r="P22">
-        <v>1.672646313333334</v>
+        <v>1.668311962333334</v>
       </c>
       <c r="Q22">
-        <v>4.592646313333334</v>
+        <v>4.588311962333334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2034232720076432</v>
+        <v>0.20490908254367</v>
       </c>
       <c r="T22">
-        <v>1.350166858333495</v>
+        <v>1.362893990044153</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.29523374241419</v>
+        <v>19.32879404039446</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1692722752094993</v>
+        <v>0.168763932812884</v>
       </c>
       <c r="C23">
-        <v>10.50677215540176</v>
+        <v>10.43404535811441</v>
       </c>
       <c r="D23">
-        <v>12.18487215540176</v>
+        <v>12.2352453581144</v>
       </c>
       <c r="E23">
-        <v>-1.0649</v>
+        <v>-0.9417999999999997</v>
       </c>
       <c r="F23">
-        <v>2.5851</v>
+        <v>2.7082</v>
       </c>
       <c r="G23">
         <v>0.907</v>
@@ -3173,28 +3173,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M23">
-        <v>0.13003053</v>
+        <v>0.13622246</v>
       </c>
       <c r="N23">
-        <v>2.383302803333334</v>
+        <v>2.377110873333334</v>
       </c>
       <c r="O23">
-        <v>0.7149908410000001</v>
+        <v>0.713133262</v>
       </c>
       <c r="P23">
-        <v>1.668311962333334</v>
+        <v>1.663977611333334</v>
       </c>
       <c r="Q23">
-        <v>4.588311962333334</v>
+        <v>4.583977611333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2049090825436699</v>
+        <v>0.2064329907857487</v>
       </c>
       <c r="T23">
-        <v>1.362893990044153</v>
+        <v>1.37594745846534</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.32879404039447</v>
+        <v>18.45021249310381</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.168763932812884</v>
+        <v>0.1682555904162688</v>
       </c>
       <c r="C24">
-        <v>10.43404535811441</v>
+        <v>10.3617367832129</v>
       </c>
       <c r="D24">
-        <v>12.2352453581144</v>
+        <v>12.2860367832129</v>
       </c>
       <c r="E24">
-        <v>-0.9417999999999997</v>
+        <v>-0.8186999999999998</v>
       </c>
       <c r="F24">
-        <v>2.7082</v>
+        <v>2.8313</v>
       </c>
       <c r="G24">
         <v>0.907</v>
@@ -3255,28 +3255,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M24">
-        <v>0.13622246</v>
+        <v>0.14241439</v>
       </c>
       <c r="N24">
-        <v>2.377110873333334</v>
+        <v>2.370918943333334</v>
       </c>
       <c r="O24">
-        <v>0.713133262</v>
+        <v>0.7112756830000001</v>
       </c>
       <c r="P24">
-        <v>1.663977611333334</v>
+        <v>1.659643260333334</v>
       </c>
       <c r="Q24">
-        <v>4.583977611333333</v>
+        <v>4.579643260333333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2064329907857487</v>
+        <v>0.2079964810600893</v>
       </c>
       <c r="T24">
-        <v>1.37594745846534</v>
+        <v>1.389339978014351</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.45021249310381</v>
+        <v>17.64802934122973</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1682555904162688</v>
+        <v>0.1677472480196535</v>
       </c>
       <c r="C25">
-        <v>10.3617367832129</v>
+        <v>10.28985166083175</v>
       </c>
       <c r="D25">
-        <v>12.2860367832129</v>
+        <v>12.33725166083175</v>
       </c>
       <c r="E25">
-        <v>-0.8186999999999998</v>
+        <v>-0.6955999999999993</v>
       </c>
       <c r="F25">
-        <v>2.8313</v>
+        <v>2.9544</v>
       </c>
       <c r="G25">
         <v>0.907</v>
@@ -3337,28 +3337,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M25">
-        <v>0.14241439</v>
+        <v>0.14860632</v>
       </c>
       <c r="N25">
-        <v>2.370918943333334</v>
+        <v>2.364727013333334</v>
       </c>
       <c r="O25">
-        <v>0.7112756830000001</v>
+        <v>0.7094181040000002</v>
       </c>
       <c r="P25">
-        <v>1.659643260333334</v>
+        <v>1.655308909333334</v>
       </c>
       <c r="Q25">
-        <v>4.579643260333333</v>
+        <v>4.575308909333334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2079964810600893</v>
+        <v>0.2096011158153336</v>
       </c>
       <c r="T25">
-        <v>1.389339978014351</v>
+        <v>1.403084932288335</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.64802934122973</v>
+        <v>16.91269478534516</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1677472480196535</v>
+        <v>0.1672389056230382</v>
       </c>
       <c r="C26">
-        <v>10.28985166083175</v>
+        <v>10.21839530867868</v>
       </c>
       <c r="D26">
-        <v>12.33725166083175</v>
+        <v>12.38889530867868</v>
       </c>
       <c r="E26">
-        <v>-0.6955999999999998</v>
+        <v>-0.5724999999999998</v>
       </c>
       <c r="F26">
-        <v>2.9544</v>
+        <v>3.0775</v>
       </c>
       <c r="G26">
         <v>0.907</v>
@@ -3419,28 +3419,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M26">
-        <v>0.14860632</v>
+        <v>0.15479825</v>
       </c>
       <c r="N26">
-        <v>2.364727013333334</v>
+        <v>2.358535083333334</v>
       </c>
       <c r="O26">
-        <v>0.7094181040000002</v>
+        <v>0.7075605250000001</v>
       </c>
       <c r="P26">
-        <v>1.655308909333334</v>
+        <v>1.650974558333334</v>
       </c>
       <c r="Q26">
-        <v>4.575308909333334</v>
+        <v>4.570974558333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2096011158153336</v>
+        <v>0.2112485408307176</v>
       </c>
       <c r="T26">
-        <v>1.403084932288335</v>
+        <v>1.417196418676293</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>16.91269478534516</v>
+        <v>16.23618699393136</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1672389056230382</v>
+        <v>0.166730563226423</v>
       </c>
       <c r="C27">
-        <v>10.21839530867868</v>
+        <v>10.14737313387525</v>
       </c>
       <c r="D27">
-        <v>12.38889530867868</v>
+        <v>12.44097313387525</v>
       </c>
       <c r="E27">
-        <v>-0.5724999999999998</v>
+        <v>-0.4493999999999998</v>
       </c>
       <c r="F27">
-        <v>3.0775</v>
+        <v>3.2006</v>
       </c>
       <c r="G27">
         <v>0.907</v>
@@ -3501,28 +3501,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M27">
-        <v>0.15479825</v>
+        <v>0.16099018</v>
       </c>
       <c r="N27">
-        <v>2.358535083333334</v>
+        <v>2.352343153333334</v>
       </c>
       <c r="O27">
-        <v>0.7075605250000001</v>
+        <v>0.7057029460000002</v>
       </c>
       <c r="P27">
-        <v>1.650974558333334</v>
+        <v>1.646640207333334</v>
       </c>
       <c r="Q27">
-        <v>4.570974558333334</v>
+        <v>4.566640207333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2112485408307176</v>
+        <v>0.2129404908465175</v>
       </c>
       <c r="T27">
-        <v>1.417196418676293</v>
+        <v>1.431689296588249</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.23618699393136</v>
+        <v>15.61171826339553</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.166730563226423</v>
+        <v>0.1662222208298077</v>
       </c>
       <c r="C28">
-        <v>10.14737313387525</v>
+        <v>10.0767906348441</v>
       </c>
       <c r="D28">
-        <v>12.44097313387525</v>
+        <v>12.4934906348441</v>
       </c>
       <c r="E28">
-        <v>-0.4493999999999998</v>
+        <v>-0.3262999999999998</v>
       </c>
       <c r="F28">
-        <v>3.2006</v>
+        <v>3.3237</v>
       </c>
       <c r="G28">
         <v>0.907</v>
@@ -3583,28 +3583,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M28">
-        <v>0.16099018</v>
+        <v>0.16718211</v>
       </c>
       <c r="N28">
-        <v>2.352343153333334</v>
+        <v>2.346151223333333</v>
       </c>
       <c r="O28">
-        <v>0.7057029460000002</v>
+        <v>0.703845367</v>
       </c>
       <c r="P28">
-        <v>1.646640207333334</v>
+        <v>1.642305856333333</v>
       </c>
       <c r="Q28">
-        <v>4.566640207333334</v>
+        <v>4.562305856333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2129404908465175</v>
+        <v>0.2146787956572708</v>
       </c>
       <c r="T28">
-        <v>1.431689296588249</v>
+        <v>1.446579239648478</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.61171826339553</v>
+        <v>15.03350647586236</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1662222208298077</v>
+        <v>0.1657138784331924</v>
       </c>
       <c r="C29">
-        <v>10.0767906348441</v>
+        <v>10.00665340324414</v>
       </c>
       <c r="D29">
-        <v>12.4934906348441</v>
+        <v>12.54645340324414</v>
       </c>
       <c r="E29">
-        <v>-0.3262999999999998</v>
+        <v>-0.2031999999999994</v>
       </c>
       <c r="F29">
-        <v>3.3237</v>
+        <v>3.4468</v>
       </c>
       <c r="G29">
         <v>0.907</v>
@@ -3665,28 +3665,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M29">
-        <v>0.16718211</v>
+        <v>0.17337404</v>
       </c>
       <c r="N29">
-        <v>2.346151223333333</v>
+        <v>2.339959293333334</v>
       </c>
       <c r="O29">
-        <v>0.703845367</v>
+        <v>0.7019877880000001</v>
       </c>
       <c r="P29">
-        <v>1.642305856333333</v>
+        <v>1.637971505333333</v>
       </c>
       <c r="Q29">
-        <v>4.562305856333333</v>
+        <v>4.557971505333334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2146787956572708</v>
+        <v>0.2164653867127673</v>
       </c>
       <c r="T29">
-        <v>1.446579239648478</v>
+        <v>1.461882792238158</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.03350647586236</v>
+        <v>14.49659553029585</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1657138784331924</v>
+        <v>0.1652055360365772</v>
       </c>
       <c r="C30">
-        <v>10.00665340324414</v>
+        <v>9.936967125955224</v>
       </c>
       <c r="D30">
-        <v>12.54645340324414</v>
+        <v>12.59986712595522</v>
       </c>
       <c r="E30">
-        <v>-0.2031999999999994</v>
+        <v>-0.08009999999999939</v>
       </c>
       <c r="F30">
-        <v>3.4468</v>
+        <v>3.5699</v>
       </c>
       <c r="G30">
         <v>0.907</v>
@@ -3747,28 +3747,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M30">
-        <v>0.17337404</v>
+        <v>0.17956597</v>
       </c>
       <c r="N30">
-        <v>2.339959293333334</v>
+        <v>2.333767363333334</v>
       </c>
       <c r="O30">
-        <v>0.7019877880000001</v>
+        <v>0.700130209</v>
       </c>
       <c r="P30">
-        <v>1.637971505333333</v>
+        <v>1.633637154333333</v>
       </c>
       <c r="Q30">
-        <v>4.557971505333334</v>
+        <v>4.553637154333334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2164653867127673</v>
+        <v>0.2183023042768693</v>
       </c>
       <c r="T30">
-        <v>1.461882792238158</v>
+        <v>1.477617430816279</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.49659553029585</v>
+        <v>13.99671292580289</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1652055360365772</v>
+        <v>0.1646971936399619</v>
       </c>
       <c r="C31">
-        <v>9.936967125955226</v>
+        <v>9.867737587113774</v>
       </c>
       <c r="D31">
-        <v>12.59986712595522</v>
+        <v>12.65373758711377</v>
       </c>
       <c r="E31">
-        <v>-0.08010000000000028</v>
+        <v>0.04300000000000015</v>
       </c>
       <c r="F31">
-        <v>3.569899999999999</v>
+        <v>3.693</v>
       </c>
       <c r="G31">
         <v>0.907</v>
@@ -3829,28 +3829,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M31">
-        <v>0.17956597</v>
+        <v>0.1857579</v>
       </c>
       <c r="N31">
-        <v>2.333767363333334</v>
+        <v>2.327575433333334</v>
       </c>
       <c r="O31">
-        <v>0.700130209</v>
+        <v>0.6982726300000001</v>
       </c>
       <c r="P31">
-        <v>1.633637154333333</v>
+        <v>1.629302803333334</v>
       </c>
       <c r="Q31">
-        <v>4.553637154333334</v>
+        <v>4.549302803333333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2183023042768693</v>
+        <v>0.2201917051999456</v>
       </c>
       <c r="T31">
-        <v>1.477617430816279</v>
+        <v>1.493801630496633</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>13.99671292580289</v>
+        <v>13.53015582827613</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1646971936399619</v>
+        <v>0.1641888512433467</v>
       </c>
       <c r="C32">
-        <v>9.867737587113774</v>
+        <v>9.798970670200728</v>
       </c>
       <c r="D32">
-        <v>12.65373758711377</v>
+        <v>12.70807067020073</v>
       </c>
       <c r="E32">
-        <v>0.04300000000000015</v>
+        <v>0.1661000000000001</v>
       </c>
       <c r="F32">
-        <v>3.693</v>
+        <v>3.8161</v>
       </c>
       <c r="G32">
         <v>0.907</v>
@@ -3911,28 +3911,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M32">
-        <v>0.1857579</v>
+        <v>0.19194983</v>
       </c>
       <c r="N32">
-        <v>2.327575433333334</v>
+        <v>2.321383503333334</v>
       </c>
       <c r="O32">
-        <v>0.6982726300000001</v>
+        <v>0.6964150510000001</v>
       </c>
       <c r="P32">
-        <v>1.629302803333334</v>
+        <v>1.624968452333333</v>
       </c>
       <c r="Q32">
-        <v>4.549302803333333</v>
+        <v>4.544968452333333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2201917051999456</v>
+        <v>0.2221358713671691</v>
       </c>
       <c r="T32">
-        <v>1.493801630496633</v>
+        <v>1.510454937414098</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.53015582827613</v>
+        <v>13.09369918865432</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1641888512433467</v>
+        <v>0.1640165088467314</v>
       </c>
       <c r="C33">
-        <v>9.798970670200728</v>
+        <v>9.694397180389743</v>
       </c>
       <c r="D33">
-        <v>12.70807067020073</v>
+        <v>12.72659718038974</v>
       </c>
       <c r="E33">
-        <v>0.1661000000000001</v>
+        <v>0.2892000000000001</v>
       </c>
       <c r="F33">
-        <v>3.8161</v>
+        <v>3.9392</v>
       </c>
       <c r="G33">
         <v>0.907</v>
@@ -3993,45 +3993,45 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M33">
-        <v>0.19194983</v>
+        <v>0.20405056</v>
       </c>
       <c r="N33">
-        <v>2.321383503333334</v>
+        <v>2.309282773333334</v>
       </c>
       <c r="O33">
-        <v>0.6964150510000001</v>
+        <v>0.6927848320000002</v>
       </c>
       <c r="P33">
-        <v>1.624968452333333</v>
+        <v>1.616497941333334</v>
       </c>
       <c r="Q33">
-        <v>4.544968452333333</v>
+        <v>4.536497941333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2221358713671691</v>
+        <v>0.224137218892252</v>
       </c>
       <c r="T33">
-        <v>1.510454937414098</v>
+        <v>1.527598047476195</v>
       </c>
       <c r="U33">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>13.09369918865432</v>
+        <v>12.31720870226151</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1640165088467314</v>
+        <v>0.1635186664501162</v>
       </c>
       <c r="C34">
-        <v>9.694397180389743</v>
+        <v>9.625119057854917</v>
       </c>
       <c r="D34">
-        <v>12.72659718038974</v>
+        <v>12.78041905785492</v>
       </c>
       <c r="E34">
-        <v>0.2892000000000001</v>
+        <v>0.4123000000000001</v>
       </c>
       <c r="F34">
-        <v>3.9392</v>
+        <v>4.0623</v>
       </c>
       <c r="G34">
         <v>0.907</v>
@@ -4075,28 +4075,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M34">
-        <v>0.20405056</v>
+        <v>0.21042714</v>
       </c>
       <c r="N34">
-        <v>2.309282773333334</v>
+        <v>2.302906193333333</v>
       </c>
       <c r="O34">
-        <v>0.6927848320000002</v>
+        <v>0.6908718580000001</v>
       </c>
       <c r="P34">
-        <v>1.616497941333334</v>
+        <v>1.612034335333334</v>
       </c>
       <c r="Q34">
-        <v>4.536497941333334</v>
+        <v>4.532034335333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.224137218892252</v>
+        <v>0.2261983081345018</v>
       </c>
       <c r="T34">
-        <v>1.527598047476195</v>
+        <v>1.545252892167011</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.31720870226151</v>
+        <v>11.94395995370813</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1635186664501162</v>
+        <v>0.1630208240535009</v>
       </c>
       <c r="C35">
-        <v>9.625119057854917</v>
+        <v>9.556298103450146</v>
       </c>
       <c r="D35">
-        <v>12.78041905785492</v>
+        <v>12.83469810345015</v>
       </c>
       <c r="E35">
-        <v>0.4123000000000001</v>
+        <v>0.5354000000000001</v>
       </c>
       <c r="F35">
-        <v>4.0623</v>
+        <v>4.1854</v>
       </c>
       <c r="G35">
         <v>0.907</v>
@@ -4157,28 +4157,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M35">
-        <v>0.21042714</v>
+        <v>0.21680372</v>
       </c>
       <c r="N35">
-        <v>2.302906193333333</v>
+        <v>2.296529613333333</v>
       </c>
       <c r="O35">
-        <v>0.6908718580000001</v>
+        <v>0.688958884</v>
       </c>
       <c r="P35">
-        <v>1.612034335333334</v>
+        <v>1.607570729333333</v>
       </c>
       <c r="Q35">
-        <v>4.532034335333334</v>
+        <v>4.527570729333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2261983081345018</v>
+        <v>0.2283218546265165</v>
       </c>
       <c r="T35">
-        <v>1.545252892167011</v>
+        <v>1.563442732151487</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.94395995370813</v>
+        <v>11.59266701389318</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1630208240535009</v>
+        <v>0.1625229816568856</v>
       </c>
       <c r="C36">
-        <v>9.556298103450146</v>
+        <v>9.487940166863478</v>
       </c>
       <c r="D36">
-        <v>12.83469810345015</v>
+        <v>12.88944016686348</v>
       </c>
       <c r="E36">
-        <v>0.5354000000000001</v>
+        <v>0.6585000000000001</v>
       </c>
       <c r="F36">
-        <v>4.1854</v>
+        <v>4.3085</v>
       </c>
       <c r="G36">
         <v>0.907</v>
@@ -4239,28 +4239,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M36">
-        <v>0.21680372</v>
+        <v>0.2231803</v>
       </c>
       <c r="N36">
-        <v>2.296529613333333</v>
+        <v>2.290153033333334</v>
       </c>
       <c r="O36">
-        <v>0.688958884</v>
+        <v>0.68704591</v>
       </c>
       <c r="P36">
-        <v>1.607570729333333</v>
+        <v>1.603107123333333</v>
       </c>
       <c r="Q36">
-        <v>4.527570729333333</v>
+        <v>4.523107123333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2283218546265165</v>
+        <v>0.2305107410105933</v>
       </c>
       <c r="T36">
-        <v>1.563442732151487</v>
+        <v>1.582192259520102</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.59266701389318</v>
+        <v>11.26144795635338</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1625229816568856</v>
+        <v>0.1620251392602703</v>
       </c>
       <c r="C37">
-        <v>9.487940166863478</v>
+        <v>9.420051198009944</v>
       </c>
       <c r="D37">
-        <v>12.88944016686348</v>
+        <v>12.94465119800994</v>
       </c>
       <c r="E37">
-        <v>0.6585000000000001</v>
+        <v>0.781600000000001</v>
       </c>
       <c r="F37">
-        <v>4.3085</v>
+        <v>4.4316</v>
       </c>
       <c r="G37">
         <v>0.907</v>
@@ -4321,28 +4321,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M37">
-        <v>0.2231803</v>
+        <v>0.22955688</v>
       </c>
       <c r="N37">
-        <v>2.290153033333334</v>
+        <v>2.283776453333334</v>
       </c>
       <c r="O37">
-        <v>0.68704591</v>
+        <v>0.685132936</v>
       </c>
       <c r="P37">
-        <v>1.603107123333333</v>
+        <v>1.598643517333334</v>
       </c>
       <c r="Q37">
-        <v>4.523107123333333</v>
+        <v>4.518643517333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2305107410105933</v>
+        <v>0.2327680300941725</v>
       </c>
       <c r="T37">
-        <v>1.582192259520102</v>
+        <v>1.601527709618986</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.26144795635338</v>
+        <v>10.94862995756578</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1620251392602704</v>
+        <v>0.1615272968636551</v>
       </c>
       <c r="C38">
-        <v>9.420051198009938</v>
+        <v>9.352637249187289</v>
       </c>
       <c r="D38">
-        <v>12.94465119800994</v>
+        <v>13.00033724918729</v>
       </c>
       <c r="E38">
-        <v>0.7816000000000001</v>
+        <v>0.9047000000000001</v>
       </c>
       <c r="F38">
-        <v>4.4316</v>
+        <v>4.5547</v>
       </c>
       <c r="G38">
         <v>0.907</v>
@@ -4403,28 +4403,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M38">
-        <v>0.22955688</v>
+        <v>0.23593346</v>
       </c>
       <c r="N38">
-        <v>2.283776453333334</v>
+        <v>2.277399873333334</v>
       </c>
       <c r="O38">
-        <v>0.685132936</v>
+        <v>0.683219962</v>
       </c>
       <c r="P38">
-        <v>1.598643517333334</v>
+        <v>1.594179911333334</v>
       </c>
       <c r="Q38">
-        <v>4.518643517333333</v>
+        <v>4.514179911333334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2327680300941725</v>
+        <v>0.2350969791486589</v>
       </c>
       <c r="T38">
-        <v>1.601527709618986</v>
+        <v>1.621476983530533</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.94862995756579</v>
+        <v>10.65272103979374</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1615272968636551</v>
+        <v>0.1610294544670399</v>
       </c>
       <c r="C39">
-        <v>9.352637249187289</v>
+        <v>9.28570447728775</v>
       </c>
       <c r="D39">
-        <v>13.00033724918729</v>
+        <v>13.05650447728775</v>
       </c>
       <c r="E39">
-        <v>0.9047000000000001</v>
+        <v>1.0278</v>
       </c>
       <c r="F39">
-        <v>4.5547</v>
+        <v>4.6778</v>
       </c>
       <c r="G39">
         <v>0.907</v>
@@ -4485,28 +4485,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M39">
-        <v>0.23593346</v>
+        <v>0.24231004</v>
       </c>
       <c r="N39">
-        <v>2.277399873333334</v>
+        <v>2.271023293333334</v>
       </c>
       <c r="O39">
-        <v>0.683219962</v>
+        <v>0.6813069880000001</v>
       </c>
       <c r="P39">
-        <v>1.594179911333334</v>
+        <v>1.589716305333333</v>
       </c>
       <c r="Q39">
-        <v>4.514179911333334</v>
+        <v>4.509716305333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2350969791486589</v>
+        <v>0.2375010555919998</v>
       </c>
       <c r="T39">
-        <v>1.621476983530533</v>
+        <v>1.642069782406969</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.65272103979374</v>
+        <v>10.37238627558864</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1610294544670399</v>
+        <v>0.1605316120704246</v>
       </c>
       <c r="C40">
-        <v>9.28570447728775</v>
+        <v>9.219259146067273</v>
       </c>
       <c r="D40">
-        <v>13.05650447728775</v>
+        <v>13.11315914606727</v>
       </c>
       <c r="E40">
-        <v>1.0278</v>
+        <v>1.1509</v>
       </c>
       <c r="F40">
-        <v>4.6778</v>
+        <v>4.8009</v>
       </c>
       <c r="G40">
         <v>0.907</v>
@@ -4567,28 +4567,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M40">
-        <v>0.24231004</v>
+        <v>0.24868662</v>
       </c>
       <c r="N40">
-        <v>2.271023293333334</v>
+        <v>2.264646713333334</v>
       </c>
       <c r="O40">
-        <v>0.6813069880000001</v>
+        <v>0.6793940140000001</v>
       </c>
       <c r="P40">
-        <v>1.589716305333333</v>
+        <v>1.585252699333334</v>
       </c>
       <c r="Q40">
-        <v>4.509716305333333</v>
+        <v>4.505252699333333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2375010555919998</v>
+        <v>0.2399839542138108</v>
       </c>
       <c r="T40">
-        <v>1.642069782406969</v>
+        <v>1.663337755017058</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.37238627558864</v>
+        <v>10.10642765313765</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1605316120704246</v>
+        <v>0.1600337696738093</v>
       </c>
       <c r="C41">
-        <v>9.219259146067273</v>
+        <v>9.153307628474156</v>
       </c>
       <c r="D41">
-        <v>13.11315914606727</v>
+        <v>13.17030762847416</v>
       </c>
       <c r="E41">
-        <v>1.1509</v>
+        <v>1.274</v>
       </c>
       <c r="F41">
-        <v>4.8009</v>
+        <v>4.923999999999999</v>
       </c>
       <c r="G41">
         <v>0.907</v>
@@ -4649,28 +4649,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M41">
-        <v>0.24868662</v>
+        <v>0.2550632</v>
       </c>
       <c r="N41">
-        <v>2.264646713333334</v>
+        <v>2.258270133333334</v>
       </c>
       <c r="O41">
-        <v>0.6793940140000001</v>
+        <v>0.6774810400000001</v>
       </c>
       <c r="P41">
-        <v>1.585252699333334</v>
+        <v>1.580789093333334</v>
       </c>
       <c r="Q41">
-        <v>4.505252699333333</v>
+        <v>4.500789093333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2399839542138108</v>
+        <v>0.2425496161230156</v>
       </c>
       <c r="T41">
-        <v>1.663337755017058</v>
+        <v>1.685314660047483</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.10642765313765</v>
+        <v>9.853766961809205</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1600337696738093</v>
+        <v>0.1600238272771941</v>
       </c>
       <c r="C42">
-        <v>9.153307628474156</v>
+        <v>9.031354012946721</v>
       </c>
       <c r="D42">
-        <v>13.17030762847416</v>
+        <v>13.17145401294672</v>
       </c>
       <c r="E42">
-        <v>1.274</v>
+        <v>1.3971</v>
       </c>
       <c r="F42">
-        <v>4.923999999999999</v>
+        <v>5.047099999999999</v>
       </c>
       <c r="G42">
         <v>0.907</v>
@@ -4731,45 +4731,45 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M42">
-        <v>0.2550632</v>
+        <v>0.27001985</v>
       </c>
       <c r="N42">
-        <v>2.258270133333334</v>
+        <v>2.243313483333334</v>
       </c>
       <c r="O42">
-        <v>0.6774810400000001</v>
+        <v>0.6729940450000002</v>
       </c>
       <c r="P42">
-        <v>1.580789093333334</v>
+        <v>1.570319438333334</v>
       </c>
       <c r="Q42">
-        <v>4.500789093333333</v>
+        <v>4.490319438333334</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2425496161230156</v>
+        <v>0.2452022496223628</v>
       </c>
       <c r="T42">
-        <v>1.685314660047483</v>
+        <v>1.708036544909449</v>
       </c>
       <c r="U42">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>9.853766961809205</v>
+        <v>9.307957668050458</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1600238272771941</v>
+        <v>0.1595378848805788</v>
       </c>
       <c r="C43">
-        <v>9.031354012946721</v>
+        <v>8.964528735627553</v>
       </c>
       <c r="D43">
-        <v>13.17145401294672</v>
+        <v>13.22772873562755</v>
       </c>
       <c r="E43">
-        <v>1.3971</v>
+        <v>1.520200000000001</v>
       </c>
       <c r="F43">
-        <v>5.047099999999999</v>
+        <v>5.1702</v>
       </c>
       <c r="G43">
         <v>0.907</v>
@@ -4813,28 +4813,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M43">
-        <v>0.27001985</v>
+        <v>0.2766057</v>
       </c>
       <c r="N43">
-        <v>2.243313483333334</v>
+        <v>2.236727633333333</v>
       </c>
       <c r="O43">
-        <v>0.6729940450000002</v>
+        <v>0.67101829</v>
       </c>
       <c r="P43">
-        <v>1.570319438333334</v>
+        <v>1.565709343333333</v>
       </c>
       <c r="Q43">
-        <v>4.490319438333334</v>
+        <v>4.485709343333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2452022496223628</v>
+        <v>0.2479463532423773</v>
       </c>
       <c r="T43">
-        <v>1.708036544909449</v>
+        <v>1.731541943042516</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.307957668050458</v>
+        <v>9.086339628334967</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1595378848805788</v>
+        <v>0.1590519424839636</v>
       </c>
       <c r="C44">
-        <v>8.964528735627551</v>
+        <v>8.898186386424381</v>
       </c>
       <c r="D44">
-        <v>13.22772873562755</v>
+        <v>13.28448638642438</v>
       </c>
       <c r="E44">
-        <v>1.5202</v>
+        <v>1.6433</v>
       </c>
       <c r="F44">
-        <v>5.170199999999999</v>
+        <v>5.293299999999999</v>
       </c>
       <c r="G44">
         <v>0.907</v>
@@ -4895,28 +4895,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M44">
-        <v>0.2766057</v>
+        <v>0.28319155</v>
       </c>
       <c r="N44">
-        <v>2.236727633333333</v>
+        <v>2.230141783333334</v>
       </c>
       <c r="O44">
-        <v>0.67101829</v>
+        <v>0.6690425350000001</v>
       </c>
       <c r="P44">
-        <v>1.565709343333333</v>
+        <v>1.561099248333334</v>
       </c>
       <c r="Q44">
-        <v>4.485709343333333</v>
+        <v>4.481099248333334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2479463532423773</v>
+        <v>0.250786741199936</v>
       </c>
       <c r="T44">
-        <v>1.731541943042516</v>
+        <v>1.75587209198727</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.086339628334969</v>
+        <v>8.875029404420204</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1590519424839636</v>
+        <v>0.1585660000873483</v>
       </c>
       <c r="C45">
-        <v>8.898186386424381</v>
+        <v>8.832333208581961</v>
       </c>
       <c r="D45">
-        <v>13.28448638642438</v>
+        <v>13.34173320858196</v>
       </c>
       <c r="E45">
-        <v>1.6433</v>
+        <v>1.7664</v>
       </c>
       <c r="F45">
-        <v>5.293299999999999</v>
+        <v>5.416399999999999</v>
       </c>
       <c r="G45">
         <v>0.907</v>
@@ -4977,28 +4977,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M45">
-        <v>0.28319155</v>
+        <v>0.2897774</v>
       </c>
       <c r="N45">
-        <v>2.230141783333334</v>
+        <v>2.223555933333333</v>
       </c>
       <c r="O45">
-        <v>0.6690425350000001</v>
+        <v>0.66706678</v>
       </c>
       <c r="P45">
-        <v>1.561099248333334</v>
+        <v>1.556489153333334</v>
       </c>
       <c r="Q45">
-        <v>4.481099248333334</v>
+        <v>4.476489153333334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.250786741199936</v>
+        <v>0.2537285715845505</v>
       </c>
       <c r="T45">
-        <v>1.75587209198727</v>
+        <v>1.781071174822908</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.875029404420204</v>
+        <v>8.673324190683378</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1585660000873483</v>
+        <v>0.1580800576907331</v>
       </c>
       <c r="C46">
-        <v>8.832333208581961</v>
+        <v>8.766975553426821</v>
       </c>
       <c r="D46">
-        <v>13.34173320858196</v>
+        <v>13.39947555342682</v>
       </c>
       <c r="E46">
-        <v>1.7664</v>
+        <v>1.8895</v>
       </c>
       <c r="F46">
-        <v>5.416399999999999</v>
+        <v>5.539499999999999</v>
       </c>
       <c r="G46">
         <v>0.907</v>
@@ -5059,28 +5059,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M46">
-        <v>0.2897774</v>
+        <v>0.29636325</v>
       </c>
       <c r="N46">
-        <v>2.223555933333333</v>
+        <v>2.216970083333334</v>
       </c>
       <c r="O46">
-        <v>0.66706678</v>
+        <v>0.6650910250000002</v>
       </c>
       <c r="P46">
-        <v>1.556489153333334</v>
+        <v>1.551879058333334</v>
       </c>
       <c r="Q46">
-        <v>4.476489153333334</v>
+        <v>4.471879058333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2537285715845505</v>
+        <v>0.2567773776195146</v>
       </c>
       <c r="T46">
-        <v>1.781071174822908</v>
+        <v>1.807186587943479</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.673324190683378</v>
+        <v>8.480583653112639</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1580800576907331</v>
+        <v>0.1575941152941178</v>
       </c>
       <c r="C47">
-        <v>8.766975553426821</v>
+        <v>8.702119882716332</v>
       </c>
       <c r="D47">
-        <v>13.39947555342682</v>
+        <v>13.45771988271633</v>
       </c>
       <c r="E47">
-        <v>1.8895</v>
+        <v>2.0126</v>
       </c>
       <c r="F47">
-        <v>5.539499999999999</v>
+        <v>5.662599999999999</v>
       </c>
       <c r="G47">
         <v>0.907</v>
@@ -5141,28 +5141,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M47">
-        <v>0.29636325</v>
+        <v>0.3029491</v>
       </c>
       <c r="N47">
-        <v>2.216970083333334</v>
+        <v>2.210384233333333</v>
       </c>
       <c r="O47">
-        <v>0.6650910250000002</v>
+        <v>0.66311527</v>
       </c>
       <c r="P47">
-        <v>1.551879058333334</v>
+        <v>1.547268963333333</v>
       </c>
       <c r="Q47">
-        <v>4.471879058333334</v>
+        <v>4.467268963333334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2567773776195146</v>
+        <v>0.2599391023965144</v>
       </c>
       <c r="T47">
-        <v>1.807186587943479</v>
+        <v>1.834269238587033</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.480583653112639</v>
+        <v>8.296223138914536</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1575941152941178</v>
+        <v>0.1571081728975025</v>
       </c>
       <c r="C48">
-        <v>8.702119882716332</v>
+        <v>8.63777277104921</v>
       </c>
       <c r="D48">
-        <v>13.45771988271633</v>
+        <v>13.51647277104921</v>
       </c>
       <c r="E48">
-        <v>2.0126</v>
+        <v>2.1357</v>
       </c>
       <c r="F48">
-        <v>5.662599999999999</v>
+        <v>5.785699999999999</v>
       </c>
       <c r="G48">
         <v>0.907</v>
@@ -5223,28 +5223,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M48">
-        <v>0.3029491</v>
+        <v>0.30953495</v>
       </c>
       <c r="N48">
-        <v>2.210384233333333</v>
+        <v>2.203798383333334</v>
       </c>
       <c r="O48">
-        <v>0.66311527</v>
+        <v>0.6611395150000001</v>
       </c>
       <c r="P48">
-        <v>1.547268963333333</v>
+        <v>1.542658868333334</v>
       </c>
       <c r="Q48">
-        <v>4.467268963333334</v>
+        <v>4.462658868333333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2599391023965144</v>
+        <v>0.2632201375424576</v>
       </c>
       <c r="T48">
-        <v>1.834269238587033</v>
+        <v>1.862373876047326</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.296223138914536</v>
+        <v>8.119707752980187</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1571081728975025</v>
+        <v>0.1566222305008872</v>
       </c>
       <c r="C49">
-        <v>8.63777277104921</v>
+        <v>8.573940908339555</v>
       </c>
       <c r="D49">
-        <v>13.51647277104921</v>
+        <v>13.57574090833956</v>
       </c>
       <c r="E49">
-        <v>2.1357</v>
+        <v>2.258800000000001</v>
       </c>
       <c r="F49">
-        <v>5.785699999999999</v>
+        <v>5.9088</v>
       </c>
       <c r="G49">
         <v>0.907</v>
@@ -5305,28 +5305,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M49">
-        <v>0.30953495</v>
+        <v>0.3161208</v>
       </c>
       <c r="N49">
-        <v>2.203798383333334</v>
+        <v>2.197212533333333</v>
       </c>
       <c r="O49">
-        <v>0.6611395150000001</v>
+        <v>0.65916376</v>
       </c>
       <c r="P49">
-        <v>1.542658868333334</v>
+        <v>1.538048773333333</v>
       </c>
       <c r="Q49">
-        <v>4.462658868333333</v>
+        <v>4.458048773333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2632201375424576</v>
+        <v>0.2666273663478601</v>
       </c>
       <c r="T49">
-        <v>1.862373876047326</v>
+        <v>1.891559461102245</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.119707752980187</v>
+        <v>7.950547174793096</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1566222305008872</v>
+        <v>0.156136288104272</v>
       </c>
       <c r="C50">
-        <v>8.573940908339557</v>
+        <v>8.510631102356164</v>
       </c>
       <c r="D50">
-        <v>13.57574090833956</v>
+        <v>13.63553110235616</v>
       </c>
       <c r="E50">
-        <v>2.2588</v>
+        <v>2.3819</v>
       </c>
       <c r="F50">
-        <v>5.908799999999999</v>
+        <v>6.031899999999999</v>
       </c>
       <c r="G50">
         <v>0.907</v>
@@ -5387,28 +5387,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M50">
-        <v>0.3161208</v>
+        <v>0.32270665</v>
       </c>
       <c r="N50">
-        <v>2.197212533333333</v>
+        <v>2.190626683333334</v>
       </c>
       <c r="O50">
-        <v>0.65916376</v>
+        <v>0.6571880050000002</v>
       </c>
       <c r="P50">
-        <v>1.538048773333333</v>
+        <v>1.533438678333334</v>
       </c>
       <c r="Q50">
-        <v>4.458048773333333</v>
+        <v>4.453438678333334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2666273663478601</v>
+        <v>0.2701682119691607</v>
       </c>
       <c r="T50">
-        <v>1.891559461102245</v>
+        <v>1.921889578904416</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.950547174793097</v>
+        <v>7.788291110001402</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.156136288104272</v>
+        <v>0.1556503457076567</v>
       </c>
       <c r="C51">
-        <v>8.510631102356164</v>
+        <v>8.447850281329297</v>
       </c>
       <c r="D51">
-        <v>13.63553110235616</v>
+        <v>13.6958502813293</v>
       </c>
       <c r="E51">
-        <v>2.3819</v>
+        <v>2.505</v>
       </c>
       <c r="F51">
-        <v>6.031899999999999</v>
+        <v>6.154999999999999</v>
       </c>
       <c r="G51">
         <v>0.907</v>
@@ -5469,28 +5469,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M51">
-        <v>0.32270665</v>
+        <v>0.3292924999999999</v>
       </c>
       <c r="N51">
-        <v>2.190626683333334</v>
+        <v>2.184040833333334</v>
       </c>
       <c r="O51">
-        <v>0.6571880050000002</v>
+        <v>0.6552122500000002</v>
       </c>
       <c r="P51">
-        <v>1.533438678333334</v>
+        <v>1.528828583333334</v>
       </c>
       <c r="Q51">
-        <v>4.453438678333334</v>
+        <v>4.448828583333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2701682119691607</v>
+        <v>0.2738506914153135</v>
       </c>
       <c r="T51">
-        <v>1.921889578904416</v>
+        <v>1.953432901418674</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.788291110001402</v>
+        <v>7.632525287801375</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1556503457076567</v>
+        <v>0.1554500033110415</v>
       </c>
       <c r="C52">
-        <v>8.447850281329297</v>
+        <v>8.349774078740971</v>
       </c>
       <c r="D52">
-        <v>13.6958502813293</v>
+        <v>13.72087407874097</v>
       </c>
       <c r="E52">
-        <v>2.505</v>
+        <v>2.6281</v>
       </c>
       <c r="F52">
-        <v>6.154999999999999</v>
+        <v>6.278099999999999</v>
       </c>
       <c r="G52">
         <v>0.907</v>
@@ -5551,45 +5551,45 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M52">
-        <v>0.3292924999999999</v>
+        <v>0.34090083</v>
       </c>
       <c r="N52">
-        <v>2.184040833333334</v>
+        <v>2.172432503333334</v>
       </c>
       <c r="O52">
-        <v>0.6552122500000002</v>
+        <v>0.6517297510000001</v>
       </c>
       <c r="P52">
-        <v>1.528828583333334</v>
+        <v>1.520702752333334</v>
       </c>
       <c r="Q52">
-        <v>4.448828583333333</v>
+        <v>4.440702752333333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2738506914153135</v>
+        <v>0.2776834761449826</v>
       </c>
       <c r="T52">
-        <v>1.953432901418674</v>
+        <v>1.986263706484534</v>
       </c>
       <c r="U52">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V52">
         <v>0.3</v>
       </c>
       <c r="W52">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y52">
-        <v>7.632525287801375</v>
+        <v>7.372623097847353</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1554500033110415</v>
+        <v>0.1549696609144262</v>
       </c>
       <c r="C53">
-        <v>8.349774078740971</v>
+        <v>8.287045407949414</v>
       </c>
       <c r="D53">
-        <v>13.72087407874097</v>
+        <v>13.78124540794941</v>
       </c>
       <c r="E53">
-        <v>2.6281</v>
+        <v>2.7512</v>
       </c>
       <c r="F53">
-        <v>6.278099999999999</v>
+        <v>6.401199999999999</v>
       </c>
       <c r="G53">
         <v>0.907</v>
@@ -5633,28 +5633,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M53">
-        <v>0.34090083</v>
+        <v>0.3475851599999999</v>
       </c>
       <c r="N53">
-        <v>2.172432503333334</v>
+        <v>2.165748173333334</v>
       </c>
       <c r="O53">
-        <v>0.6517297510000001</v>
+        <v>0.6497244520000001</v>
       </c>
       <c r="P53">
-        <v>1.520702752333334</v>
+        <v>1.516023721333334</v>
       </c>
       <c r="Q53">
-        <v>4.440702752333333</v>
+        <v>4.436023721333333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2776834761449826</v>
+        <v>0.281675960238388</v>
       </c>
       <c r="T53">
-        <v>1.986263706484534</v>
+        <v>2.020462461761471</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.372623097847353</v>
+        <v>7.230841884427212</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1549696609144262</v>
+        <v>0.1544893185178109</v>
       </c>
       <c r="C54">
-        <v>8.287045407949414</v>
+        <v>8.22485034817602</v>
       </c>
       <c r="D54">
-        <v>13.78124540794941</v>
+        <v>13.84215034817602</v>
       </c>
       <c r="E54">
-        <v>2.7512</v>
+        <v>2.8743</v>
       </c>
       <c r="F54">
-        <v>6.401199999999999</v>
+        <v>6.524299999999999</v>
       </c>
       <c r="G54">
         <v>0.907</v>
@@ -5715,28 +5715,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M54">
-        <v>0.3475851599999999</v>
+        <v>0.35426949</v>
       </c>
       <c r="N54">
-        <v>2.165748173333334</v>
+        <v>2.159063843333334</v>
       </c>
       <c r="O54">
-        <v>0.6497244520000001</v>
+        <v>0.647719153</v>
       </c>
       <c r="P54">
-        <v>1.516023721333334</v>
+        <v>1.511344690333333</v>
       </c>
       <c r="Q54">
-        <v>4.436023721333333</v>
+        <v>4.431344690333333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.281675960238388</v>
+        <v>0.2858383372719382</v>
       </c>
       <c r="T54">
-        <v>2.020462461761471</v>
+        <v>2.056116483220406</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.230841884427212</v>
+        <v>7.094410905475755</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1544893185178109</v>
+        <v>0.1540089761211957</v>
       </c>
       <c r="C55">
-        <v>8.22485034817602</v>
+        <v>8.163196005559419</v>
       </c>
       <c r="D55">
-        <v>13.84215034817602</v>
+        <v>13.90359600555942</v>
       </c>
       <c r="E55">
-        <v>2.8743</v>
+        <v>2.9974</v>
       </c>
       <c r="F55">
-        <v>6.524299999999999</v>
+        <v>6.647399999999999</v>
       </c>
       <c r="G55">
         <v>0.907</v>
@@ -5797,28 +5797,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M55">
-        <v>0.35426949</v>
+        <v>0.36095382</v>
       </c>
       <c r="N55">
-        <v>2.159063843333334</v>
+        <v>2.152379513333334</v>
       </c>
       <c r="O55">
-        <v>0.647719153</v>
+        <v>0.6457138540000001</v>
       </c>
       <c r="P55">
-        <v>1.511344690333333</v>
+        <v>1.506665659333334</v>
       </c>
       <c r="Q55">
-        <v>4.431344690333333</v>
+        <v>4.426665659333334</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2858383372719382</v>
+        <v>0.2901816872199907</v>
       </c>
       <c r="T55">
-        <v>2.056116483220406</v>
+        <v>2.093320679525382</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.094410905475755</v>
+        <v>6.963032925744723</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1540089761211957</v>
+        <v>0.1535286337245804</v>
       </c>
       <c r="C56">
-        <v>8.163196005559419</v>
+        <v>8.102089612978176</v>
       </c>
       <c r="D56">
-        <v>13.90359600555942</v>
+        <v>13.96558961297818</v>
       </c>
       <c r="E56">
-        <v>2.9974</v>
+        <v>3.120500000000001</v>
       </c>
       <c r="F56">
-        <v>6.647399999999999</v>
+        <v>6.7705</v>
       </c>
       <c r="G56">
         <v>0.907</v>
@@ -5879,28 +5879,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M56">
-        <v>0.36095382</v>
+        <v>0.36763815</v>
       </c>
       <c r="N56">
-        <v>2.152379513333334</v>
+        <v>2.145695183333334</v>
       </c>
       <c r="O56">
-        <v>0.6457138540000001</v>
+        <v>0.6437085550000001</v>
       </c>
       <c r="P56">
-        <v>1.506665659333334</v>
+        <v>1.501986628333334</v>
       </c>
       <c r="Q56">
-        <v>4.426665659333334</v>
+        <v>4.421986628333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2901816872199907</v>
+        <v>0.2947180749435121</v>
       </c>
       <c r="T56">
-        <v>2.093320679525382</v>
+        <v>2.132178395666134</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.963032925744723</v>
+        <v>6.836432327094818</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1535286337245804</v>
+        <v>0.1530482913279652</v>
       </c>
       <c r="C57">
-        <v>8.102089612978176</v>
+        <v>8.041538532888975</v>
       </c>
       <c r="D57">
-        <v>13.96558961297818</v>
+        <v>14.02813853288897</v>
       </c>
       <c r="E57">
-        <v>3.120500000000001</v>
+        <v>3.243600000000001</v>
       </c>
       <c r="F57">
-        <v>6.7705</v>
+        <v>6.8936</v>
       </c>
       <c r="G57">
         <v>0.907</v>
@@ -5961,28 +5961,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M57">
-        <v>0.36763815</v>
+        <v>0.37432248</v>
       </c>
       <c r="N57">
-        <v>2.145695183333334</v>
+        <v>2.139010853333334</v>
       </c>
       <c r="O57">
-        <v>0.6437085550000001</v>
+        <v>0.6417032560000001</v>
       </c>
       <c r="P57">
-        <v>1.501986628333334</v>
+        <v>1.497307597333334</v>
       </c>
       <c r="Q57">
-        <v>4.421986628333333</v>
+        <v>4.417307597333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2947180749435121</v>
+        <v>0.2994606621090118</v>
       </c>
       <c r="T57">
-        <v>2.132178395666134</v>
+        <v>2.172802371631466</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.836432327094818</v>
+        <v>6.714353178396696</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1530482913279652</v>
+        <v>0.1525679489313499</v>
       </c>
       <c r="C58">
-        <v>8.041538532888975</v>
+        <v>7.981550260241454</v>
       </c>
       <c r="D58">
-        <v>14.02813853288897</v>
+        <v>14.09125026024145</v>
       </c>
       <c r="E58">
-        <v>3.243600000000001</v>
+        <v>3.366700000000001</v>
       </c>
       <c r="F58">
-        <v>6.8936</v>
+        <v>7.0167</v>
       </c>
       <c r="G58">
         <v>0.907</v>
@@ -6043,28 +6043,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M58">
-        <v>0.37432248</v>
+        <v>0.38100681</v>
       </c>
       <c r="N58">
-        <v>2.139010853333334</v>
+        <v>2.132326523333334</v>
       </c>
       <c r="O58">
-        <v>0.6417032560000001</v>
+        <v>0.639697957</v>
       </c>
       <c r="P58">
-        <v>1.497307597333334</v>
+        <v>1.492628566333333</v>
       </c>
       <c r="Q58">
-        <v>4.417307597333334</v>
+        <v>4.412628566333334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2994606621090118</v>
+        <v>0.3044238347240696</v>
       </c>
       <c r="T58">
-        <v>2.172802371631466</v>
+        <v>2.215315834850999</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.714353178396696</v>
+        <v>6.596557508600262</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1525679489313499</v>
+        <v>0.1520876065347347</v>
       </c>
       <c r="C59">
-        <v>7.981550260241454</v>
+        <v>7.922132425472053</v>
       </c>
       <c r="D59">
-        <v>14.09125026024145</v>
+        <v>14.15493242547205</v>
       </c>
       <c r="E59">
-        <v>3.366700000000001</v>
+        <v>3.489800000000001</v>
       </c>
       <c r="F59">
-        <v>7.0167</v>
+        <v>7.1398</v>
       </c>
       <c r="G59">
         <v>0.907</v>
@@ -6125,28 +6125,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M59">
-        <v>0.38100681</v>
+        <v>0.38769114</v>
       </c>
       <c r="N59">
-        <v>2.132326523333334</v>
+        <v>2.125642193333334</v>
       </c>
       <c r="O59">
-        <v>0.639697957</v>
+        <v>0.6376926580000001</v>
       </c>
       <c r="P59">
-        <v>1.492628566333333</v>
+        <v>1.487949535333334</v>
       </c>
       <c r="Q59">
-        <v>4.412628566333334</v>
+        <v>4.407949535333334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3044238347240696</v>
+        <v>0.3096233488922254</v>
       </c>
       <c r="T59">
-        <v>2.215315834850999</v>
+        <v>2.259853748700035</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.596557508600262</v>
+        <v>6.482823758451983</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1520876065347347</v>
+        <v>0.1516072641381194</v>
       </c>
       <c r="C60">
-        <v>7.922132425472054</v>
+        <v>7.863292797579423</v>
       </c>
       <c r="D60">
-        <v>14.15493242547205</v>
+        <v>14.21919279757942</v>
       </c>
       <c r="E60">
-        <v>3.489799999999999</v>
+        <v>3.6129</v>
       </c>
       <c r="F60">
-        <v>7.139799999999998</v>
+        <v>7.262899999999999</v>
       </c>
       <c r="G60">
         <v>0.907</v>
@@ -6207,28 +6207,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M60">
-        <v>0.3876911399999999</v>
+        <v>0.39437547</v>
       </c>
       <c r="N60">
-        <v>2.125642193333334</v>
+        <v>2.118957863333334</v>
       </c>
       <c r="O60">
-        <v>0.6376926580000001</v>
+        <v>0.6356873590000001</v>
       </c>
       <c r="P60">
-        <v>1.487949535333334</v>
+        <v>1.483270504333334</v>
       </c>
       <c r="Q60">
-        <v>4.407949535333334</v>
+        <v>4.403270504333333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3096233488922254</v>
+        <v>0.3150764978978522</v>
       </c>
       <c r="T60">
-        <v>2.259853748700034</v>
+        <v>2.306564243712436</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.482823758451984</v>
+        <v>6.372945389664661</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1516072641381194</v>
+        <v>0.1511269217415041</v>
       </c>
       <c r="C61">
-        <v>7.863292797579423</v>
+        <v>7.805039287283988</v>
       </c>
       <c r="D61">
-        <v>14.21919279757942</v>
+        <v>14.28403928728399</v>
       </c>
       <c r="E61">
-        <v>3.6129</v>
+        <v>3.736</v>
       </c>
       <c r="F61">
-        <v>7.262899999999999</v>
+        <v>7.385999999999999</v>
       </c>
       <c r="G61">
         <v>0.907</v>
@@ -6289,28 +6289,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M61">
-        <v>0.39437547</v>
+        <v>0.4010598</v>
       </c>
       <c r="N61">
-        <v>2.118957863333334</v>
+        <v>2.112273533333334</v>
       </c>
       <c r="O61">
-        <v>0.6356873590000001</v>
+        <v>0.63368206</v>
       </c>
       <c r="P61">
-        <v>1.483270504333334</v>
+        <v>1.478591473333334</v>
       </c>
       <c r="Q61">
-        <v>4.403270504333333</v>
+        <v>4.398591473333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3150764978978522</v>
+        <v>0.3208023043537603</v>
       </c>
       <c r="T61">
-        <v>2.306564243712436</v>
+        <v>2.355610263475459</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.372945389664661</v>
+        <v>6.266729633170249</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1511269217415041</v>
+        <v>0.1506465793448889</v>
       </c>
       <c r="C62">
-        <v>7.805039287283988</v>
+        <v>7.747379950274344</v>
       </c>
       <c r="D62">
-        <v>14.28403928728399</v>
+        <v>14.34947995027434</v>
       </c>
       <c r="E62">
-        <v>3.736</v>
+        <v>3.8591</v>
       </c>
       <c r="F62">
-        <v>7.385999999999999</v>
+        <v>7.509099999999999</v>
       </c>
       <c r="G62">
         <v>0.907</v>
@@ -6371,28 +6371,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M62">
-        <v>0.4010598</v>
+        <v>0.40774413</v>
       </c>
       <c r="N62">
-        <v>2.112273533333334</v>
+        <v>2.105589203333333</v>
       </c>
       <c r="O62">
-        <v>0.63368206</v>
+        <v>0.631676761</v>
       </c>
       <c r="P62">
-        <v>1.478591473333334</v>
+        <v>1.473912442333333</v>
       </c>
       <c r="Q62">
-        <v>4.398591473333333</v>
+        <v>4.393912442333333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3208023043537603</v>
+        <v>0.3268217419099715</v>
       </c>
       <c r="T62">
-        <v>2.355610263475459</v>
+        <v>2.40717146373915</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.266729633170249</v>
+        <v>6.163996360495327</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1506465793448889</v>
+        <v>0.1506002369482736</v>
       </c>
       <c r="C63">
-        <v>7.747379950274344</v>
+        <v>7.630625253590845</v>
       </c>
       <c r="D63">
-        <v>14.34947995027434</v>
+        <v>14.35582525359084</v>
       </c>
       <c r="E63">
-        <v>3.8591</v>
+        <v>3.9822</v>
       </c>
       <c r="F63">
-        <v>7.509099999999999</v>
+        <v>7.632199999999999</v>
       </c>
       <c r="G63">
         <v>0.907</v>
@@ -6453,45 +6453,45 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M63">
-        <v>0.40774413</v>
+        <v>0.42206066</v>
       </c>
       <c r="N63">
-        <v>2.105589203333333</v>
+        <v>2.091272673333334</v>
       </c>
       <c r="O63">
-        <v>0.631676761</v>
+        <v>0.627381802</v>
       </c>
       <c r="P63">
-        <v>1.473912442333333</v>
+        <v>1.463890871333334</v>
       </c>
       <c r="Q63">
-        <v>4.393912442333333</v>
+        <v>4.383890871333334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3268217419099715</v>
+        <v>0.3331579919691411</v>
       </c>
       <c r="T63">
-        <v>2.40717146373915</v>
+        <v>2.46144641138514</v>
       </c>
       <c r="U63">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V63">
         <v>0.3</v>
       </c>
       <c r="W63">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>6.163996360495327</v>
+        <v>5.954910209668283</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1506002369482736</v>
+        <v>0.1501268945516584</v>
       </c>
       <c r="C64">
-        <v>7.630625253590845</v>
+        <v>7.572659184396763</v>
       </c>
       <c r="D64">
-        <v>14.35582525359084</v>
+        <v>14.42095918439676</v>
       </c>
       <c r="E64">
-        <v>3.9822</v>
+        <v>4.1053</v>
       </c>
       <c r="F64">
-        <v>7.632199999999999</v>
+        <v>7.755299999999999</v>
       </c>
       <c r="G64">
         <v>0.907</v>
@@ -6535,28 +6535,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M64">
-        <v>0.42206066</v>
+        <v>0.42886809</v>
       </c>
       <c r="N64">
-        <v>2.091272673333334</v>
+        <v>2.084465243333334</v>
       </c>
       <c r="O64">
-        <v>0.627381802</v>
+        <v>0.6253395730000001</v>
       </c>
       <c r="P64">
-        <v>1.463890871333334</v>
+        <v>1.459125670333334</v>
       </c>
       <c r="Q64">
-        <v>4.383890871333334</v>
+        <v>4.379125670333334</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3331579919691411</v>
+        <v>0.3398367420315092</v>
       </c>
       <c r="T64">
-        <v>2.46144641138514</v>
+        <v>2.518655139984967</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.954910209668283</v>
+        <v>5.860387825387834</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1501268945516584</v>
+        <v>0.1496535521550431</v>
       </c>
       <c r="C65">
-        <v>7.572659184396763</v>
+        <v>7.515286848402354</v>
       </c>
       <c r="D65">
-        <v>14.42095918439676</v>
+        <v>14.48668684840235</v>
       </c>
       <c r="E65">
-        <v>4.1053</v>
+        <v>4.2284</v>
       </c>
       <c r="F65">
-        <v>7.755299999999999</v>
+        <v>7.878399999999999</v>
       </c>
       <c r="G65">
         <v>0.907</v>
@@ -6617,28 +6617,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M65">
-        <v>0.42886809</v>
+        <v>0.43567552</v>
       </c>
       <c r="N65">
-        <v>2.084465243333334</v>
+        <v>2.077657813333333</v>
       </c>
       <c r="O65">
-        <v>0.6253395730000001</v>
+        <v>0.623297344</v>
       </c>
       <c r="P65">
-        <v>1.459125670333334</v>
+        <v>1.454360469333333</v>
       </c>
       <c r="Q65">
-        <v>4.379125670333334</v>
+        <v>4.374360469333333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3398367420315092</v>
+        <v>0.3468865337640087</v>
       </c>
       <c r="T65">
-        <v>2.518655139984967</v>
+        <v>2.579042131284785</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.860387825387834</v>
+        <v>5.768819265616148</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1496535521550431</v>
+        <v>0.1491802097584278</v>
       </c>
       <c r="C66">
-        <v>7.515286848402354</v>
+        <v>7.458516401107472</v>
       </c>
       <c r="D66">
-        <v>14.48668684840235</v>
+        <v>14.55301640110747</v>
       </c>
       <c r="E66">
-        <v>4.2284</v>
+        <v>4.351500000000001</v>
       </c>
       <c r="F66">
-        <v>7.878399999999999</v>
+        <v>8.0015</v>
       </c>
       <c r="G66">
         <v>0.907</v>
@@ -6699,28 +6699,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M66">
-        <v>0.43567552</v>
+        <v>0.44248295</v>
       </c>
       <c r="N66">
-        <v>2.077657813333333</v>
+        <v>2.070850383333334</v>
       </c>
       <c r="O66">
-        <v>0.623297344</v>
+        <v>0.6212551150000001</v>
       </c>
       <c r="P66">
-        <v>1.454360469333333</v>
+        <v>1.449595268333334</v>
       </c>
       <c r="Q66">
-        <v>4.374360469333333</v>
+        <v>4.369595268333334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3468865337640087</v>
+        <v>0.3543391707383653</v>
       </c>
       <c r="T66">
-        <v>2.579042131284785</v>
+        <v>2.642879807801735</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.768819265616148</v>
+        <v>5.680068199991284</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1491802097584278</v>
+        <v>0.1487068673618126</v>
       </c>
       <c r="C67">
-        <v>7.458516401107472</v>
+        <v>7.402356148063923</v>
       </c>
       <c r="D67">
-        <v>14.55301640110747</v>
+        <v>14.61995614806392</v>
       </c>
       <c r="E67">
-        <v>4.351500000000001</v>
+        <v>4.4746</v>
       </c>
       <c r="F67">
-        <v>8.0015</v>
+        <v>8.124599999999999</v>
       </c>
       <c r="G67">
         <v>0.907</v>
@@ -6781,28 +6781,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M67">
-        <v>0.44248295</v>
+        <v>0.44929038</v>
       </c>
       <c r="N67">
-        <v>2.070850383333334</v>
+        <v>2.064042953333334</v>
       </c>
       <c r="O67">
-        <v>0.6212551150000001</v>
+        <v>0.6192128860000001</v>
       </c>
       <c r="P67">
-        <v>1.449595268333334</v>
+        <v>1.444830067333334</v>
       </c>
       <c r="Q67">
-        <v>4.369595268333334</v>
+        <v>4.364830067333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3543391707383653</v>
+        <v>0.3622301981229782</v>
       </c>
       <c r="T67">
-        <v>2.642879807801735</v>
+        <v>2.710472641760859</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.680068199991284</v>
+        <v>5.594006560597478</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1487068673618126</v>
+        <v>0.1482335249651973</v>
       </c>
       <c r="C68">
-        <v>7.402356148063923</v>
+        <v>7.346814548342403</v>
       </c>
       <c r="D68">
-        <v>14.61995614806392</v>
+        <v>14.6875145483424</v>
       </c>
       <c r="E68">
-        <v>4.4746</v>
+        <v>4.597700000000001</v>
       </c>
       <c r="F68">
-        <v>8.124599999999999</v>
+        <v>8.2477</v>
       </c>
       <c r="G68">
         <v>0.907</v>
@@ -6863,28 +6863,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M68">
-        <v>0.44929038</v>
+        <v>0.45609781</v>
       </c>
       <c r="N68">
-        <v>2.064042953333334</v>
+        <v>2.057235523333333</v>
       </c>
       <c r="O68">
-        <v>0.6192128860000001</v>
+        <v>0.6171706570000001</v>
       </c>
       <c r="P68">
-        <v>1.444830067333334</v>
+        <v>1.440064866333334</v>
       </c>
       <c r="Q68">
-        <v>4.364830067333333</v>
+        <v>4.360064866333333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3622301981229782</v>
+        <v>0.3705994695915071</v>
       </c>
       <c r="T68">
-        <v>2.710472641760859</v>
+        <v>2.782162011111445</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.594006560597478</v>
+        <v>5.510513925364679</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1482335249651973</v>
+        <v>0.1477601825685821</v>
       </c>
       <c r="C69">
-        <v>7.346814548342403</v>
+        <v>7.291900218095961</v>
       </c>
       <c r="D69">
-        <v>14.6875145483424</v>
+        <v>14.75570021809596</v>
       </c>
       <c r="E69">
-        <v>4.597700000000001</v>
+        <v>4.7208</v>
       </c>
       <c r="F69">
-        <v>8.2477</v>
+        <v>8.370799999999999</v>
       </c>
       <c r="G69">
         <v>0.907</v>
@@ -6945,28 +6945,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M69">
-        <v>0.45609781</v>
+        <v>0.46290524</v>
       </c>
       <c r="N69">
-        <v>2.057235523333333</v>
+        <v>2.050428093333334</v>
       </c>
       <c r="O69">
-        <v>0.6171706570000001</v>
+        <v>0.6151284280000001</v>
       </c>
       <c r="P69">
-        <v>1.440064866333334</v>
+        <v>1.435299665333333</v>
       </c>
       <c r="Q69">
-        <v>4.360064866333333</v>
+        <v>4.355299665333334</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3705994695915071</v>
+        <v>0.3794918205268191</v>
       </c>
       <c r="T69">
-        <v>2.782162011111445</v>
+        <v>2.858331966046442</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.510513925364679</v>
+        <v>5.429476955874022</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1477601825685821</v>
+        <v>0.1472868401719668</v>
       </c>
       <c r="C70">
-        <v>7.291900218095961</v>
+        <v>7.237621934223242</v>
       </c>
       <c r="D70">
-        <v>14.75570021809596</v>
+        <v>14.82452193422324</v>
       </c>
       <c r="E70">
-        <v>4.7208</v>
+        <v>4.843900000000001</v>
       </c>
       <c r="F70">
-        <v>8.370799999999999</v>
+        <v>8.4939</v>
       </c>
       <c r="G70">
         <v>0.907</v>
@@ -7027,28 +7027,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M70">
-        <v>0.46290524</v>
+        <v>0.46971267</v>
       </c>
       <c r="N70">
-        <v>2.050428093333334</v>
+        <v>2.043620663333334</v>
       </c>
       <c r="O70">
-        <v>0.6151284280000001</v>
+        <v>0.6130861990000002</v>
       </c>
       <c r="P70">
-        <v>1.435299665333333</v>
+        <v>1.430534464333334</v>
       </c>
       <c r="Q70">
-        <v>4.355299665333334</v>
+        <v>4.350534464333334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3794918205268191</v>
+        <v>0.3889578715224737</v>
       </c>
       <c r="T70">
-        <v>2.858331966046442</v>
+        <v>2.939416111622407</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.429476955874022</v>
+        <v>5.350788884049761</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1472868401719668</v>
+        <v>0.1468134977753515</v>
       </c>
       <c r="C71">
-        <v>7.237621934223242</v>
+        <v>7.183988638134702</v>
       </c>
       <c r="D71">
-        <v>14.82452193422324</v>
+        <v>14.8939886381347</v>
       </c>
       <c r="E71">
-        <v>4.843900000000001</v>
+        <v>4.967</v>
       </c>
       <c r="F71">
-        <v>8.4939</v>
+        <v>8.616999999999999</v>
       </c>
       <c r="G71">
         <v>0.907</v>
@@ -7109,28 +7109,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M71">
-        <v>0.46971267</v>
+        <v>0.4765200999999999</v>
       </c>
       <c r="N71">
-        <v>2.043620663333334</v>
+        <v>2.036813233333334</v>
       </c>
       <c r="O71">
-        <v>0.6130861990000002</v>
+        <v>0.61104397</v>
       </c>
       <c r="P71">
-        <v>1.430534464333334</v>
+        <v>1.425769263333334</v>
       </c>
       <c r="Q71">
-        <v>4.350534464333334</v>
+        <v>4.345769263333334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3889578715224737</v>
+        <v>0.3990549925845053</v>
       </c>
       <c r="T71">
-        <v>2.939416111622407</v>
+        <v>3.025905866903436</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.350788884049761</v>
+        <v>5.27434904284905</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1468134977753515</v>
+        <v>0.1463401553787363</v>
       </c>
       <c r="C72">
-        <v>7.183988638134702</v>
+        <v>7.131009439625187</v>
       </c>
       <c r="D72">
-        <v>14.8939886381347</v>
+        <v>14.96410943962519</v>
       </c>
       <c r="E72">
-        <v>4.967</v>
+        <v>5.090100000000001</v>
       </c>
       <c r="F72">
-        <v>8.616999999999999</v>
+        <v>8.7401</v>
       </c>
       <c r="G72">
         <v>0.907</v>
@@ -7191,28 +7191,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M72">
-        <v>0.4765200999999999</v>
+        <v>0.48332753</v>
       </c>
       <c r="N72">
-        <v>2.036813233333334</v>
+        <v>2.030005803333334</v>
       </c>
       <c r="O72">
-        <v>0.61104397</v>
+        <v>0.609001741</v>
       </c>
       <c r="P72">
-        <v>1.425769263333334</v>
+        <v>1.421004062333334</v>
       </c>
       <c r="Q72">
-        <v>4.345769263333334</v>
+        <v>4.341004062333333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3990549925845053</v>
+        <v>0.4098484668232287</v>
       </c>
       <c r="T72">
-        <v>3.025905866903436</v>
+        <v>3.118360432893502</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.27434904284905</v>
+        <v>5.20006243661174</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1463401553787363</v>
+        <v>0.145866812982121</v>
       </c>
       <c r="C73">
-        <v>7.131009439625188</v>
+        <v>7.078693620856491</v>
       </c>
       <c r="D73">
-        <v>14.96410943962519</v>
+        <v>15.03489362085649</v>
       </c>
       <c r="E73">
-        <v>5.090099999999999</v>
+        <v>5.2132</v>
       </c>
       <c r="F73">
-        <v>8.740099999999998</v>
+        <v>8.863199999999999</v>
       </c>
       <c r="G73">
         <v>0.907</v>
@@ -7273,28 +7273,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M73">
-        <v>0.4833275299999999</v>
+        <v>0.49013496</v>
       </c>
       <c r="N73">
-        <v>2.030005803333334</v>
+        <v>2.023198373333334</v>
       </c>
       <c r="O73">
-        <v>0.609001741</v>
+        <v>0.6069595120000001</v>
       </c>
       <c r="P73">
-        <v>1.421004062333334</v>
+        <v>1.416238861333334</v>
       </c>
       <c r="Q73">
-        <v>4.341004062333333</v>
+        <v>4.336238861333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4098484668232286</v>
+        <v>0.4214129035075751</v>
       </c>
       <c r="T73">
-        <v>3.118360432893501</v>
+        <v>3.217418896454286</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.200062436611741</v>
+        <v>5.127839347214355</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.145866812982121</v>
+        <v>0.1453934705855058</v>
       </c>
       <c r="C74">
-        <v>7.078693620856491</v>
+        <v>7.027050640453391</v>
       </c>
       <c r="D74">
-        <v>15.03489362085649</v>
+        <v>15.10635064045339</v>
       </c>
       <c r="E74">
-        <v>5.2132</v>
+        <v>5.336299999999999</v>
       </c>
       <c r="F74">
-        <v>8.863199999999999</v>
+        <v>8.986299999999998</v>
       </c>
       <c r="G74">
         <v>0.907</v>
@@ -7355,28 +7355,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M74">
-        <v>0.49013496</v>
+        <v>0.4969423899999999</v>
       </c>
       <c r="N74">
-        <v>2.023198373333334</v>
+        <v>2.016390943333334</v>
       </c>
       <c r="O74">
-        <v>0.6069595120000001</v>
+        <v>0.604917283</v>
       </c>
       <c r="P74">
-        <v>1.416238861333334</v>
+        <v>1.411473660333334</v>
       </c>
       <c r="Q74">
-        <v>4.336238861333333</v>
+        <v>4.331473660333334</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4214129035075751</v>
+        <v>0.4338339651315029</v>
       </c>
       <c r="T74">
-        <v>3.217418896454286</v>
+        <v>3.323815023982536</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.127839347214355</v>
+        <v>5.05759497259498</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1453934705855058</v>
+        <v>0.1449201281888905</v>
       </c>
       <c r="C75">
-        <v>7.027050640453391</v>
+        <v>6.976090137717117</v>
       </c>
       <c r="D75">
-        <v>15.10635064045339</v>
+        <v>15.17849013771712</v>
       </c>
       <c r="E75">
-        <v>5.336299999999999</v>
+        <v>5.4594</v>
       </c>
       <c r="F75">
-        <v>8.986299999999998</v>
+        <v>9.109399999999999</v>
       </c>
       <c r="G75">
         <v>0.907</v>
@@ -7437,28 +7437,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M75">
-        <v>0.4969423899999999</v>
+        <v>0.50374982</v>
       </c>
       <c r="N75">
-        <v>2.016390943333334</v>
+        <v>2.009583513333334</v>
       </c>
       <c r="O75">
-        <v>0.604917283</v>
+        <v>0.6028750540000001</v>
       </c>
       <c r="P75">
-        <v>1.411473660333334</v>
+        <v>1.406708459333334</v>
       </c>
       <c r="Q75">
-        <v>4.331473660333334</v>
+        <v>4.326708459333334</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4338339651315029</v>
+        <v>0.4472104930341942</v>
       </c>
       <c r="T75">
-        <v>3.323815023982536</v>
+        <v>3.438395469012959</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.05759497259498</v>
+        <v>4.989249094586939</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1449201281888905</v>
+        <v>0.1444467857922753</v>
       </c>
       <c r="C76">
-        <v>6.976090137717117</v>
+        <v>6.925821936960094</v>
       </c>
       <c r="D76">
-        <v>15.17849013771712</v>
+        <v>15.25132193696009</v>
       </c>
       <c r="E76">
-        <v>5.4594</v>
+        <v>5.582499999999999</v>
       </c>
       <c r="F76">
-        <v>9.109399999999999</v>
+        <v>9.232499999999998</v>
       </c>
       <c r="G76">
         <v>0.907</v>
@@ -7519,28 +7519,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M76">
-        <v>0.50374982</v>
+        <v>0.51055725</v>
       </c>
       <c r="N76">
-        <v>2.009583513333334</v>
+        <v>2.002776083333334</v>
       </c>
       <c r="O76">
-        <v>0.6028750540000001</v>
+        <v>0.6008328250000001</v>
       </c>
       <c r="P76">
-        <v>1.406708459333334</v>
+        <v>1.401943258333334</v>
       </c>
       <c r="Q76">
-        <v>4.326708459333334</v>
+        <v>4.321943258333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4472104930341942</v>
+        <v>0.461657143169101</v>
       </c>
       <c r="T76">
-        <v>3.438395469012959</v>
+        <v>3.562142349645816</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.989249094586939</v>
+        <v>4.922725773325781</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1444467857922753</v>
+        <v>0.14397344339566</v>
       </c>
       <c r="C77">
-        <v>6.925821936960094</v>
+        <v>6.876256051966092</v>
       </c>
       <c r="D77">
-        <v>15.25132193696009</v>
+        <v>15.32485605196609</v>
       </c>
       <c r="E77">
-        <v>5.582499999999999</v>
+        <v>5.7056</v>
       </c>
       <c r="F77">
-        <v>9.232499999999998</v>
+        <v>9.355599999999999</v>
       </c>
       <c r="G77">
         <v>0.907</v>
@@ -7601,28 +7601,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M77">
-        <v>0.51055725</v>
+        <v>0.5173646799999999</v>
       </c>
       <c r="N77">
-        <v>2.002776083333334</v>
+        <v>1.995968653333334</v>
       </c>
       <c r="O77">
-        <v>0.6008328250000001</v>
+        <v>0.5987905960000001</v>
       </c>
       <c r="P77">
-        <v>1.401943258333334</v>
+        <v>1.397178057333333</v>
       </c>
       <c r="Q77">
-        <v>4.321943258333333</v>
+        <v>4.317178057333333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.461657143169101</v>
+        <v>0.47730768081525</v>
       </c>
       <c r="T77">
-        <v>3.562142349645816</v>
+        <v>3.696201470331412</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.922725773325781</v>
+        <v>4.85795306578202</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.14397344339566</v>
+        <v>0.1435001009990448</v>
       </c>
       <c r="C78">
-        <v>6.876256051966092</v>
+        <v>6.827402690580033</v>
       </c>
       <c r="D78">
-        <v>15.32485605196609</v>
+        <v>15.39910269058003</v>
       </c>
       <c r="E78">
-        <v>5.7056</v>
+        <v>5.8287</v>
       </c>
       <c r="F78">
-        <v>9.355599999999999</v>
+        <v>9.4787</v>
       </c>
       <c r="G78">
         <v>0.907</v>
@@ -7683,28 +7683,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M78">
-        <v>0.5173646799999999</v>
+        <v>0.52417211</v>
       </c>
       <c r="N78">
-        <v>1.995968653333334</v>
+        <v>1.989161223333334</v>
       </c>
       <c r="O78">
-        <v>0.5987905960000001</v>
+        <v>0.5967483670000001</v>
       </c>
       <c r="P78">
-        <v>1.397178057333333</v>
+        <v>1.392412856333334</v>
       </c>
       <c r="Q78">
-        <v>4.317178057333333</v>
+        <v>4.312412856333333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.47730768081525</v>
+        <v>0.4943191347784555</v>
       </c>
       <c r="T78">
-        <v>3.696201470331412</v>
+        <v>3.841917905859233</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.85795306578202</v>
+        <v>4.79486276622641</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1435001009990448</v>
+        <v>0.1430267586024295</v>
       </c>
       <c r="C79">
-        <v>6.827402690580033</v>
+        <v>6.779272259431851</v>
       </c>
       <c r="D79">
-        <v>15.39910269058003</v>
+        <v>15.47407225943185</v>
       </c>
       <c r="E79">
-        <v>5.8287</v>
+        <v>5.9518</v>
       </c>
       <c r="F79">
-        <v>9.4787</v>
+        <v>9.601799999999999</v>
       </c>
       <c r="G79">
         <v>0.907</v>
@@ -7765,28 +7765,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M79">
-        <v>0.52417211</v>
+        <v>0.5309795399999999</v>
       </c>
       <c r="N79">
-        <v>1.989161223333334</v>
+        <v>1.982353793333334</v>
       </c>
       <c r="O79">
-        <v>0.5967483670000001</v>
+        <v>0.5947061380000001</v>
       </c>
       <c r="P79">
-        <v>1.392412856333334</v>
+        <v>1.387647655333334</v>
       </c>
       <c r="Q79">
-        <v>4.312412856333333</v>
+        <v>4.307647655333334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4943191347784555</v>
+        <v>0.5128770845564976</v>
       </c>
       <c r="T79">
-        <v>3.841917905859233</v>
+        <v>4.000881290071401</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.79486276622641</v>
+        <v>4.733390166659404</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1430267586024295</v>
+        <v>0.1425534162058142</v>
       </c>
       <c r="C80">
-        <v>6.779272259431851</v>
+        <v>6.731875368799029</v>
       </c>
       <c r="D80">
-        <v>15.47407225943185</v>
+        <v>15.54977536879903</v>
       </c>
       <c r="E80">
-        <v>5.9518</v>
+        <v>6.0749</v>
       </c>
       <c r="F80">
-        <v>9.601799999999999</v>
+        <v>9.7249</v>
       </c>
       <c r="G80">
         <v>0.907</v>
@@ -7847,28 +7847,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M80">
-        <v>0.5309795399999999</v>
+        <v>0.53778697</v>
       </c>
       <c r="N80">
-        <v>1.982353793333334</v>
+        <v>1.975546363333334</v>
       </c>
       <c r="O80">
-        <v>0.5947061380000001</v>
+        <v>0.5926639090000001</v>
       </c>
       <c r="P80">
-        <v>1.387647655333334</v>
+        <v>1.382882454333334</v>
       </c>
       <c r="Q80">
-        <v>4.307647655333334</v>
+        <v>4.302882454333334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5128770845564976</v>
+        <v>0.5332024581229249</v>
       </c>
       <c r="T80">
-        <v>4.000881290071401</v>
+        <v>4.174984044208538</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.733390166659404</v>
+        <v>4.673473835435868</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1425534162058142</v>
+        <v>0.1420800738091989</v>
       </c>
       <c r="C81">
-        <v>6.731875368799029</v>
+        <v>6.685222837612596</v>
       </c>
       <c r="D81">
-        <v>15.54977536879903</v>
+        <v>15.62622283761259</v>
       </c>
       <c r="E81">
-        <v>6.0749</v>
+        <v>6.198</v>
       </c>
       <c r="F81">
-        <v>9.7249</v>
+        <v>9.847999999999999</v>
       </c>
       <c r="G81">
         <v>0.907</v>
@@ -7929,28 +7929,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M81">
-        <v>0.53778697</v>
+        <v>0.5445943999999999</v>
       </c>
       <c r="N81">
-        <v>1.975546363333334</v>
+        <v>1.968738933333334</v>
       </c>
       <c r="O81">
-        <v>0.5926639090000001</v>
+        <v>0.5906216800000001</v>
       </c>
       <c r="P81">
-        <v>1.382882454333334</v>
+        <v>1.378117253333334</v>
       </c>
       <c r="Q81">
-        <v>4.302882454333334</v>
+        <v>4.298117253333333</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5332024581229249</v>
+        <v>0.5555603690459948</v>
       </c>
       <c r="T81">
-        <v>4.174984044208538</v>
+        <v>4.366497073759389</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.673473835435868</v>
+        <v>4.61505541249292</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1420800738091989</v>
+        <v>0.1416067314125837</v>
       </c>
       <c r="C82">
-        <v>6.685222837612596</v>
+        <v>6.639325698611437</v>
       </c>
       <c r="D82">
-        <v>15.62622283761259</v>
+        <v>15.70342569861144</v>
       </c>
       <c r="E82">
-        <v>6.198</v>
+        <v>6.3211</v>
       </c>
       <c r="F82">
-        <v>9.847999999999999</v>
+        <v>9.9711</v>
       </c>
       <c r="G82">
         <v>0.907</v>
@@ -8011,28 +8011,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M82">
-        <v>0.5445943999999999</v>
+        <v>0.55140183</v>
       </c>
       <c r="N82">
-        <v>1.968738933333334</v>
+        <v>1.961931503333334</v>
       </c>
       <c r="O82">
-        <v>0.5906216800000001</v>
+        <v>0.5885794510000001</v>
       </c>
       <c r="P82">
-        <v>1.378117253333334</v>
+        <v>1.373352052333333</v>
       </c>
       <c r="Q82">
-        <v>4.298117253333333</v>
+        <v>4.293352052333333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5555603690459948</v>
+        <v>0.5802717442767564</v>
       </c>
       <c r="T82">
-        <v>4.366497073759389</v>
+        <v>4.57816936957875</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.61505541249292</v>
+        <v>4.558079419746093</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1416067314125837</v>
+        <v>0.1411333890159684</v>
       </c>
       <c r="C83">
-        <v>6.639325698611437</v>
+        <v>6.594195203650282</v>
       </c>
       <c r="D83">
-        <v>15.70342569861144</v>
+        <v>15.78139520365028</v>
       </c>
       <c r="E83">
-        <v>6.3211</v>
+        <v>6.444199999999999</v>
       </c>
       <c r="F83">
-        <v>9.9711</v>
+        <v>10.0942</v>
       </c>
       <c r="G83">
         <v>0.907</v>
@@ -8093,28 +8093,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M83">
-        <v>0.55140183</v>
+        <v>0.5582092599999999</v>
       </c>
       <c r="N83">
-        <v>1.961931503333334</v>
+        <v>1.955124073333334</v>
       </c>
       <c r="O83">
-        <v>0.5885794510000001</v>
+        <v>0.5865372220000001</v>
       </c>
       <c r="P83">
-        <v>1.373352052333333</v>
+        <v>1.368586851333334</v>
       </c>
       <c r="Q83">
-        <v>4.293352052333333</v>
+        <v>4.288586851333333</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5802717442767564</v>
+        <v>0.6077288278664915</v>
       </c>
       <c r="T83">
-        <v>4.57816936957875</v>
+        <v>4.81336080937804</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.558079419746093</v>
+        <v>4.502493085358946</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1411333890159684</v>
+        <v>0.1421125466193532</v>
       </c>
       <c r="C84">
-        <v>6.594195203650282</v>
+        <v>6.310654288649411</v>
       </c>
       <c r="D84">
-        <v>15.78139520365028</v>
+        <v>15.62095428864941</v>
       </c>
       <c r="E84">
-        <v>6.444199999999999</v>
+        <v>6.5673</v>
       </c>
       <c r="F84">
-        <v>10.0942</v>
+        <v>10.2173</v>
       </c>
       <c r="G84">
         <v>0.907</v>
@@ -8175,45 +8175,45 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M84">
-        <v>0.5582092599999999</v>
+        <v>0.59055994</v>
       </c>
       <c r="N84">
-        <v>1.955124073333334</v>
+        <v>1.922773393333334</v>
       </c>
       <c r="O84">
-        <v>0.5865372220000001</v>
+        <v>0.5768320180000001</v>
       </c>
       <c r="P84">
-        <v>1.368586851333334</v>
+        <v>1.345941375333334</v>
       </c>
       <c r="Q84">
-        <v>4.288586851333333</v>
+        <v>4.265941375333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6077288278664915</v>
+        <v>0.6384161565844306</v>
       </c>
       <c r="T84">
-        <v>4.81336080937804</v>
+        <v>5.076221830330188</v>
       </c>
       <c r="U84">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V84">
         <v>0.3</v>
       </c>
       <c r="W84">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y84">
-        <v>4.502493085358946</v>
+        <v>4.255847989508624</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1421125466193532</v>
+        <v>0.1416567042227379</v>
       </c>
       <c r="C85">
-        <v>6.310654288649411</v>
+        <v>6.261839058797657</v>
       </c>
       <c r="D85">
-        <v>15.62095428864941</v>
+        <v>15.69523905879766</v>
       </c>
       <c r="E85">
-        <v>6.5673</v>
+        <v>6.690400000000001</v>
       </c>
       <c r="F85">
-        <v>10.2173</v>
+        <v>10.3404</v>
       </c>
       <c r="G85">
         <v>0.907</v>
@@ -8257,28 +8257,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M85">
-        <v>0.59055994</v>
+        <v>0.5976751200000001</v>
       </c>
       <c r="N85">
-        <v>1.922773393333334</v>
+        <v>1.915658213333334</v>
       </c>
       <c r="O85">
-        <v>0.5768320180000001</v>
+        <v>0.574697464</v>
       </c>
       <c r="P85">
-        <v>1.345941375333334</v>
+        <v>1.340960749333334</v>
       </c>
       <c r="Q85">
-        <v>4.265941375333334</v>
+        <v>4.260960749333334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6384161565844306</v>
+        <v>0.6729394013921124</v>
       </c>
       <c r="T85">
-        <v>5.076221830330188</v>
+        <v>5.371940478901355</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.255847989508624</v>
+        <v>4.205183132490664</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1416567042227379</v>
+        <v>0.1412008618261227</v>
       </c>
       <c r="C86">
-        <v>6.261839058797658</v>
+        <v>6.2137337208066</v>
       </c>
       <c r="D86">
-        <v>15.69523905879766</v>
+        <v>15.7702337208066</v>
       </c>
       <c r="E86">
-        <v>6.690399999999999</v>
+        <v>6.813499999999999</v>
       </c>
       <c r="F86">
-        <v>10.3404</v>
+        <v>10.4635</v>
       </c>
       <c r="G86">
         <v>0.907</v>
@@ -8339,28 +8339,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M86">
-        <v>0.59767512</v>
+        <v>0.6047902999999999</v>
       </c>
       <c r="N86">
-        <v>1.915658213333334</v>
+        <v>1.908543033333334</v>
       </c>
       <c r="O86">
-        <v>0.5746974640000001</v>
+        <v>0.5725629100000001</v>
       </c>
       <c r="P86">
-        <v>1.340960749333334</v>
+        <v>1.335980123333333</v>
       </c>
       <c r="Q86">
-        <v>4.260960749333334</v>
+        <v>4.255980123333334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6729394013921119</v>
+        <v>0.7120657455074844</v>
       </c>
       <c r="T86">
-        <v>5.371940478901352</v>
+        <v>5.70708828061534</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.205183132490665</v>
+        <v>4.15571038975548</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1412008618261227</v>
+        <v>0.1407450194295074</v>
       </c>
       <c r="C87">
-        <v>6.2137337208066</v>
+        <v>6.166348499503473</v>
       </c>
       <c r="D87">
-        <v>15.7702337208066</v>
+        <v>15.84594849950347</v>
       </c>
       <c r="E87">
-        <v>6.813499999999999</v>
+        <v>6.936599999999999</v>
       </c>
       <c r="F87">
-        <v>10.4635</v>
+        <v>10.5866</v>
       </c>
       <c r="G87">
         <v>0.907</v>
@@ -8421,28 +8421,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M87">
-        <v>0.6047902999999999</v>
+        <v>0.61190548</v>
       </c>
       <c r="N87">
-        <v>1.908543033333334</v>
+        <v>1.901427853333334</v>
       </c>
       <c r="O87">
-        <v>0.5725629100000001</v>
+        <v>0.5704283560000001</v>
       </c>
       <c r="P87">
-        <v>1.335980123333333</v>
+        <v>1.330999497333334</v>
       </c>
       <c r="Q87">
-        <v>4.255980123333334</v>
+        <v>4.250999497333334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7120657455074844</v>
+        <v>0.7567815673536241</v>
       </c>
       <c r="T87">
-        <v>5.70708828061534</v>
+        <v>6.09011433971704</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.15571038975548</v>
+        <v>4.107388175921114</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1407450194295074</v>
+        <v>0.1402891770328921</v>
       </c>
       <c r="C88">
-        <v>6.166348499503473</v>
+        <v>6.119693817025301</v>
       </c>
       <c r="D88">
-        <v>15.84594849950347</v>
+        <v>15.9223938170253</v>
       </c>
       <c r="E88">
-        <v>6.936599999999999</v>
+        <v>7.059699999999999</v>
       </c>
       <c r="F88">
-        <v>10.5866</v>
+        <v>10.7097</v>
       </c>
       <c r="G88">
         <v>0.907</v>
@@ -8503,28 +8503,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M88">
-        <v>0.61190548</v>
+        <v>0.6190206599999999</v>
       </c>
       <c r="N88">
-        <v>1.901427853333334</v>
+        <v>1.894312673333334</v>
       </c>
       <c r="O88">
-        <v>0.5704283560000001</v>
+        <v>0.5682938020000001</v>
       </c>
       <c r="P88">
-        <v>1.330999497333334</v>
+        <v>1.326018871333334</v>
       </c>
       <c r="Q88">
-        <v>4.250999497333334</v>
+        <v>4.246018871333334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7567815673536241</v>
+        <v>0.8083767464068626</v>
       </c>
       <c r="T88">
-        <v>6.09011433971704</v>
+        <v>6.532067484834388</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.107388175921114</v>
+        <v>4.060176817577194</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1402891770328921</v>
+        <v>0.1398333346362769</v>
       </c>
       <c r="C89">
-        <v>6.119693817025301</v>
+        <v>6.073780297601356</v>
       </c>
       <c r="D89">
-        <v>15.9223938170253</v>
+        <v>15.99958029760136</v>
       </c>
       <c r="E89">
-        <v>7.059699999999999</v>
+        <v>7.182799999999999</v>
       </c>
       <c r="F89">
-        <v>10.7097</v>
+        <v>10.8328</v>
       </c>
       <c r="G89">
         <v>0.907</v>
@@ -8585,28 +8585,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M89">
-        <v>0.6190206599999999</v>
+        <v>0.62613584</v>
       </c>
       <c r="N89">
-        <v>1.894312673333334</v>
+        <v>1.887197493333334</v>
       </c>
       <c r="O89">
-        <v>0.5682938020000001</v>
+        <v>0.5661592480000001</v>
       </c>
       <c r="P89">
-        <v>1.326018871333334</v>
+        <v>1.321038245333334</v>
       </c>
       <c r="Q89">
-        <v>4.246018871333334</v>
+        <v>4.241038245333334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8083767464068626</v>
+        <v>0.8685711219689741</v>
       </c>
       <c r="T89">
-        <v>6.532067484834388</v>
+        <v>7.047679487471294</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.060176817577194</v>
+        <v>4.014038444650179</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1398333346362769</v>
+        <v>0.1415579922396616</v>
       </c>
       <c r="C90">
-        <v>6.073780297601356</v>
+        <v>5.662518472506257</v>
       </c>
       <c r="D90">
-        <v>15.99958029760136</v>
+        <v>15.71141847250626</v>
       </c>
       <c r="E90">
-        <v>7.182799999999999</v>
+        <v>7.3059</v>
       </c>
       <c r="F90">
-        <v>10.8328</v>
+        <v>10.9559</v>
       </c>
       <c r="G90">
         <v>0.907</v>
@@ -8667,45 +8667,45 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M90">
-        <v>0.62613584</v>
+        <v>0.67159667</v>
       </c>
       <c r="N90">
-        <v>1.887197493333334</v>
+        <v>1.841736663333334</v>
       </c>
       <c r="O90">
-        <v>0.5661592480000001</v>
+        <v>0.5525209990000001</v>
       </c>
       <c r="P90">
-        <v>1.321038245333334</v>
+        <v>1.289215664333334</v>
       </c>
       <c r="Q90">
-        <v>4.241038245333334</v>
+        <v>4.209215664333334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8685711219689741</v>
+        <v>0.9397099294514695</v>
       </c>
       <c r="T90">
-        <v>7.047679487471294</v>
+        <v>7.657039126951273</v>
       </c>
       <c r="U90">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V90">
         <v>0.3</v>
       </c>
       <c r="W90">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y90">
-        <v>4.014038444650179</v>
+        <v>3.74232548433174</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1415579922396616</v>
+        <v>0.1411266498430463</v>
       </c>
       <c r="C91">
-        <v>5.662518472506257</v>
+        <v>5.610510878557607</v>
       </c>
       <c r="D91">
-        <v>15.71141847250626</v>
+        <v>15.78251087855761</v>
       </c>
       <c r="E91">
-        <v>7.3059</v>
+        <v>7.428999999999999</v>
       </c>
       <c r="F91">
-        <v>10.9559</v>
+        <v>11.079</v>
       </c>
       <c r="G91">
         <v>0.907</v>
@@ -8749,28 +8749,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M91">
-        <v>0.67159667</v>
+        <v>0.6791427</v>
       </c>
       <c r="N91">
-        <v>1.841736663333334</v>
+        <v>1.834190633333334</v>
       </c>
       <c r="O91">
-        <v>0.5525209990000001</v>
+        <v>0.5502571900000001</v>
       </c>
       <c r="P91">
-        <v>1.289215664333334</v>
+        <v>1.283933443333334</v>
       </c>
       <c r="Q91">
-        <v>4.209215664333334</v>
+        <v>4.203933443333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9397099294514695</v>
+        <v>1.025076498430464</v>
       </c>
       <c r="T91">
-        <v>7.657039126951273</v>
+        <v>8.388270694327247</v>
       </c>
       <c r="U91">
         <v>0.0613</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.74232548433174</v>
+        <v>3.700744090061387</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1411266498430463</v>
+        <v>0.1406953074464311</v>
       </c>
       <c r="C92">
-        <v>5.610510878557607</v>
+        <v>5.559149579344327</v>
       </c>
       <c r="D92">
-        <v>15.78251087855761</v>
+        <v>15.85424957934433</v>
       </c>
       <c r="E92">
-        <v>7.428999999999999</v>
+        <v>7.5521</v>
       </c>
       <c r="F92">
-        <v>11.079</v>
+        <v>11.2021</v>
       </c>
       <c r="G92">
         <v>0.907</v>
@@ -8831,28 +8831,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M92">
-        <v>0.6791427</v>
+        <v>0.68668873</v>
       </c>
       <c r="N92">
-        <v>1.834190633333334</v>
+        <v>1.826644603333334</v>
       </c>
       <c r="O92">
-        <v>0.5502571900000001</v>
+        <v>0.5479933810000001</v>
       </c>
       <c r="P92">
-        <v>1.283933443333334</v>
+        <v>1.278651222333334</v>
       </c>
       <c r="Q92">
-        <v>4.203933443333334</v>
+        <v>4.198651222333334</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.025076498430464</v>
+        <v>1.129413416071457</v>
       </c>
       <c r="T92">
-        <v>8.388270694327247</v>
+        <v>9.28199816556455</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.700744090061387</v>
+        <v>3.660076572588185</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1406953074464311</v>
+        <v>0.1402639650498159</v>
       </c>
       <c r="C93">
-        <v>5.559149579344327</v>
+        <v>5.508443428220819</v>
       </c>
       <c r="D93">
-        <v>15.85424957934433</v>
+        <v>15.92664342822082</v>
       </c>
       <c r="E93">
-        <v>7.5521</v>
+        <v>7.675199999999999</v>
       </c>
       <c r="F93">
-        <v>11.2021</v>
+        <v>11.3252</v>
       </c>
       <c r="G93">
         <v>0.907</v>
@@ -8913,28 +8913,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M93">
-        <v>0.68668873</v>
+        <v>0.69423476</v>
       </c>
       <c r="N93">
-        <v>1.826644603333334</v>
+        <v>1.819098573333334</v>
       </c>
       <c r="O93">
-        <v>0.5479933810000001</v>
+        <v>0.5457295720000001</v>
       </c>
       <c r="P93">
-        <v>1.278651222333334</v>
+        <v>1.273369001333334</v>
       </c>
       <c r="Q93">
-        <v>4.198651222333334</v>
+        <v>4.193369001333334</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.129413416071457</v>
+        <v>1.259834563122699</v>
       </c>
       <c r="T93">
-        <v>9.28199816556455</v>
+        <v>10.39915750461118</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.660076572588185</v>
+        <v>3.620293131581792</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1402639650498159</v>
+        <v>0.1398326226532006</v>
       </c>
       <c r="C94">
-        <v>5.508443428220819</v>
+        <v>5.458401440988386</v>
       </c>
       <c r="D94">
-        <v>15.92664342822082</v>
+        <v>15.99970144098839</v>
       </c>
       <c r="E94">
-        <v>7.675199999999999</v>
+        <v>7.7983</v>
       </c>
       <c r="F94">
-        <v>11.3252</v>
+        <v>11.4483</v>
       </c>
       <c r="G94">
         <v>0.907</v>
@@ -8995,28 +8995,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M94">
-        <v>0.69423476</v>
+        <v>0.7017807899999999</v>
       </c>
       <c r="N94">
-        <v>1.819098573333334</v>
+        <v>1.811552543333334</v>
       </c>
       <c r="O94">
-        <v>0.5457295720000001</v>
+        <v>0.543465763</v>
       </c>
       <c r="P94">
-        <v>1.273369001333334</v>
+        <v>1.268086780333334</v>
       </c>
       <c r="Q94">
-        <v>4.193369001333334</v>
+        <v>4.188086780333334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.259834563122699</v>
+        <v>1.427518895045724</v>
       </c>
       <c r="T94">
-        <v>10.39915750461118</v>
+        <v>11.83550522624256</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.620293131581792</v>
+        <v>3.581365248446504</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1398326226532006</v>
+        <v>0.1394012802565853</v>
       </c>
       <c r="C95">
-        <v>5.458401440988386</v>
+        <v>5.409032799638252</v>
       </c>
       <c r="D95">
-        <v>15.99970144098839</v>
+        <v>16.07343279963825</v>
       </c>
       <c r="E95">
-        <v>7.7983</v>
+        <v>7.921399999999999</v>
       </c>
       <c r="F95">
-        <v>11.4483</v>
+        <v>11.5714</v>
       </c>
       <c r="G95">
         <v>0.907</v>
@@ -9077,28 +9077,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M95">
-        <v>0.7017807899999999</v>
+        <v>0.7093268199999999</v>
       </c>
       <c r="N95">
-        <v>1.811552543333334</v>
+        <v>1.804006513333334</v>
       </c>
       <c r="O95">
-        <v>0.543465763</v>
+        <v>0.5412019540000002</v>
       </c>
       <c r="P95">
-        <v>1.268086780333334</v>
+        <v>1.262804559333334</v>
       </c>
       <c r="Q95">
-        <v>4.188086780333334</v>
+        <v>4.182804559333333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.427518895045724</v>
+        <v>1.651098004276424</v>
       </c>
       <c r="T95">
-        <v>11.83550522624256</v>
+        <v>13.75063552175107</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.581365248446504</v>
+        <v>3.543265618143882</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1394012802565853</v>
+        <v>0.1389699378599701</v>
       </c>
       <c r="C96">
-        <v>5.409032799638252</v>
+        <v>5.360346856198534</v>
       </c>
       <c r="D96">
-        <v>16.07343279963825</v>
+        <v>16.14784685619853</v>
       </c>
       <c r="E96">
-        <v>7.921399999999999</v>
+        <v>8.044499999999999</v>
       </c>
       <c r="F96">
-        <v>11.5714</v>
+        <v>11.6945</v>
       </c>
       <c r="G96">
         <v>0.907</v>
@@ -9159,28 +9159,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M96">
-        <v>0.7093268199999999</v>
+        <v>0.71687285</v>
       </c>
       <c r="N96">
-        <v>1.804006513333334</v>
+        <v>1.796460483333334</v>
       </c>
       <c r="O96">
-        <v>0.5412019540000002</v>
+        <v>0.538938145</v>
       </c>
       <c r="P96">
-        <v>1.262804559333334</v>
+        <v>1.257522338333334</v>
       </c>
       <c r="Q96">
-        <v>4.182804559333333</v>
+        <v>4.177522338333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.651098004276424</v>
+        <v>1.964108757199404</v>
       </c>
       <c r="T96">
-        <v>13.75063552175107</v>
+        <v>16.43181793546298</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.543265618143882</v>
+        <v>3.505968085321314</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1389699378599701</v>
+        <v>0.1404201954633548</v>
       </c>
       <c r="C97">
-        <v>5.360346856198534</v>
+        <v>4.98974644080821</v>
       </c>
       <c r="D97">
-        <v>16.14784685619853</v>
+        <v>15.90034644080821</v>
       </c>
       <c r="E97">
-        <v>8.044499999999999</v>
+        <v>8.1676</v>
       </c>
       <c r="F97">
-        <v>11.6945</v>
+        <v>11.8176</v>
       </c>
       <c r="G97">
         <v>0.907</v>
@@ -9241,45 +9241,45 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M97">
-        <v>0.71687285</v>
+        <v>0.7575081600000001</v>
       </c>
       <c r="N97">
-        <v>1.796460483333334</v>
+        <v>1.755825173333334</v>
       </c>
       <c r="O97">
-        <v>0.538938145</v>
+        <v>0.5267475520000001</v>
       </c>
       <c r="P97">
-        <v>1.257522338333334</v>
+        <v>1.229077621333333</v>
       </c>
       <c r="Q97">
-        <v>4.177522338333334</v>
+        <v>4.149077621333333</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.964108757199404</v>
+        <v>2.433624886583875</v>
       </c>
       <c r="T97">
-        <v>16.43181793546298</v>
+        <v>20.45359155603086</v>
       </c>
       <c r="U97">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V97">
         <v>0.3</v>
       </c>
       <c r="W97">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y97">
-        <v>3.505968085321314</v>
+        <v>3.317896051883234</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1404201954633548</v>
+        <v>0.1400084530667396</v>
       </c>
       <c r="C98">
-        <v>4.989746440808212</v>
+        <v>4.936139639533311</v>
       </c>
       <c r="D98">
-        <v>15.90034644080821</v>
+        <v>15.96983963953331</v>
       </c>
       <c r="E98">
-        <v>8.1676</v>
+        <v>8.290699999999998</v>
       </c>
       <c r="F98">
-        <v>11.8176</v>
+        <v>11.9407</v>
       </c>
       <c r="G98">
         <v>0.907</v>
@@ -9323,28 +9323,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M98">
-        <v>0.75750816</v>
+        <v>0.76539887</v>
       </c>
       <c r="N98">
-        <v>1.755825173333334</v>
+        <v>1.747934463333334</v>
       </c>
       <c r="O98">
-        <v>0.5267475520000001</v>
+        <v>0.5243803390000001</v>
       </c>
       <c r="P98">
-        <v>1.229077621333333</v>
+        <v>1.223554124333334</v>
       </c>
       <c r="Q98">
-        <v>4.149077621333333</v>
+        <v>4.143554124333334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.433624886583869</v>
+        <v>3.216151768891316</v>
       </c>
       <c r="T98">
-        <v>20.4535915560308</v>
+        <v>27.15654759031056</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.317896051883235</v>
+        <v>3.283690937946294</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1400084530667396</v>
+        <v>0.1395967106701243</v>
       </c>
       <c r="C99">
-        <v>4.936139639533311</v>
+        <v>4.883142951256771</v>
       </c>
       <c r="D99">
-        <v>15.96983963953331</v>
+        <v>16.03994295125677</v>
       </c>
       <c r="E99">
-        <v>8.290699999999998</v>
+        <v>8.413799999999998</v>
       </c>
       <c r="F99">
-        <v>11.9407</v>
+        <v>12.0638</v>
       </c>
       <c r="G99">
         <v>0.907</v>
@@ -9405,28 +9405,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M99">
-        <v>0.76539887</v>
+        <v>0.7732895799999999</v>
       </c>
       <c r="N99">
-        <v>1.747934463333334</v>
+        <v>1.740043753333334</v>
       </c>
       <c r="O99">
-        <v>0.5243803390000001</v>
+        <v>0.522013126</v>
       </c>
       <c r="P99">
-        <v>1.223554124333334</v>
+        <v>1.218030627333334</v>
       </c>
       <c r="Q99">
-        <v>4.143554124333334</v>
+        <v>4.138030627333333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.216151768891316</v>
+        <v>4.781205533506211</v>
       </c>
       <c r="T99">
-        <v>27.15654759031056</v>
+        <v>40.56245965887007</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.283690937946294</v>
+        <v>3.250183887559087</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1395967106701243</v>
+        <v>0.139184968273509</v>
       </c>
       <c r="C100">
-        <v>4.883142951256771</v>
+        <v>4.830764446101419</v>
       </c>
       <c r="D100">
-        <v>16.03994295125677</v>
+        <v>16.11066444610142</v>
       </c>
       <c r="E100">
-        <v>8.413799999999998</v>
+        <v>8.536899999999999</v>
       </c>
       <c r="F100">
-        <v>12.0638</v>
+        <v>12.1869</v>
       </c>
       <c r="G100">
         <v>0.907</v>
@@ -9487,28 +9487,28 @@
         <v>2.513333333333334</v>
       </c>
       <c r="M100">
-        <v>0.7732895799999999</v>
+        <v>0.7811802899999999</v>
       </c>
       <c r="N100">
-        <v>1.740043753333334</v>
+        <v>1.732153043333334</v>
       </c>
       <c r="O100">
-        <v>0.522013126</v>
+        <v>0.5196459130000001</v>
       </c>
       <c r="P100">
-        <v>1.218030627333334</v>
+        <v>1.212507130333333</v>
       </c>
       <c r="Q100">
-        <v>4.138030627333333</v>
+        <v>4.132507130333334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.781205533506211</v>
+        <v>9.476366827350896</v>
       </c>
       <c r="T100">
-        <v>40.56245965887007</v>
+        <v>80.78019586454862</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.250183887559087</v>
+        <v>3.217353747280713</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.139184968273509</v>
-      </c>
-      <c r="C101">
-        <v>4.830764446101419</v>
-      </c>
-      <c r="D101">
-        <v>16.11066444610142</v>
-      </c>
-      <c r="E101">
-        <v>8.536899999999999</v>
-      </c>
-      <c r="F101">
-        <v>12.1869</v>
-      </c>
-      <c r="G101">
-        <v>0.907</v>
-      </c>
-      <c r="H101">
-        <v>8.66</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.433333333333334</v>
-      </c>
-      <c r="K101">
-        <v>2.92</v>
-      </c>
-      <c r="L101">
-        <v>2.513333333333334</v>
-      </c>
-      <c r="M101">
-        <v>0.7811802899999999</v>
-      </c>
-      <c r="N101">
-        <v>1.732153043333334</v>
-      </c>
-      <c r="O101">
-        <v>0.5196459130000001</v>
-      </c>
-      <c r="P101">
-        <v>1.212507130333333</v>
-      </c>
-      <c r="Q101">
-        <v>4.132507130333334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.476366827350896</v>
-      </c>
-      <c r="T101">
-        <v>80.78019586454862</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.04487</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.217353747280713</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
